--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -888,6 +888,1374 @@
         <v>646</v>
       </c>
     </row>
+    <row r="100">
+      <c r="B100" s="7">
+        <v>480</v>
+      </c>
+      <c r="C100" s="8">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="7">
+        <v>140</v>
+      </c>
+      <c r="C101" s="8">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="7">
+        <v>140</v>
+      </c>
+      <c r="C102" s="8">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="7">
+        <v>140</v>
+      </c>
+      <c r="C103" s="8">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="7">
+        <v>363</v>
+      </c>
+      <c r="C104" s="8">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="7">
+        <v>55</v>
+      </c>
+      <c r="C105" s="8">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="7">
+        <v>55</v>
+      </c>
+      <c r="C106" s="8">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="7">
+        <v>255</v>
+      </c>
+      <c r="C107" s="8">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="7">
+        <v>22</v>
+      </c>
+      <c r="C108" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="7">
+        <v>22</v>
+      </c>
+      <c r="C109" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="7">
+        <v>22</v>
+      </c>
+      <c r="C110" s="8">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="7">
+        <v>458</v>
+      </c>
+      <c r="C111" s="8">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="7">
+        <v>22</v>
+      </c>
+      <c r="C112" s="8">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="7">
+        <v>166</v>
+      </c>
+      <c r="C113" s="8">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="7">
+        <v>22</v>
+      </c>
+      <c r="C114" s="8">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="7">
+        <v>264</v>
+      </c>
+      <c r="C115" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="7">
+        <v>22</v>
+      </c>
+      <c r="C116" s="8">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="7">
+        <v>22</v>
+      </c>
+      <c r="C117" s="8">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="7">
+        <v>10</v>
+      </c>
+      <c r="C118" s="8">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="7">
+        <v>22</v>
+      </c>
+      <c r="C119" s="8">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="7">
+        <v>264</v>
+      </c>
+      <c r="C120" s="8">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="7">
+        <v>22</v>
+      </c>
+      <c r="C121" s="8">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="7">
+        <v>24</v>
+      </c>
+      <c r="C122" s="8">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="7">
+        <v>145</v>
+      </c>
+      <c r="C123" s="8">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="7">
+        <v>145</v>
+      </c>
+      <c r="C124" s="8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="7">
+        <v>205</v>
+      </c>
+      <c r="C125" s="8">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="7">
+        <v>145</v>
+      </c>
+      <c r="C126" s="8">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="7">
+        <v>145</v>
+      </c>
+      <c r="C127" s="8">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="7">
+        <v>145</v>
+      </c>
+      <c r="C128" s="8">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="7">
+        <v>43</v>
+      </c>
+      <c r="C129" s="8">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="7">
+        <v>43</v>
+      </c>
+      <c r="C130" s="8">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="7">
+        <v>32</v>
+      </c>
+      <c r="C131" s="8">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="7">
+        <v>59</v>
+      </c>
+      <c r="C132" s="8">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="7">
+        <v>49</v>
+      </c>
+      <c r="C133" s="8">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="7">
+        <v>56</v>
+      </c>
+      <c r="C134" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="7">
+        <v>35</v>
+      </c>
+      <c r="C135" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="7">
+        <v>248</v>
+      </c>
+      <c r="C136" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="7">
+        <v>16</v>
+      </c>
+      <c r="C137" s="8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="7">
+        <v>71</v>
+      </c>
+      <c r="C138" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="7">
+        <v>485</v>
+      </c>
+      <c r="C139" s="8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="7">
+        <v>59</v>
+      </c>
+      <c r="C140" s="8">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="7">
+        <v>135</v>
+      </c>
+      <c r="C141" s="8">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="7">
+        <v>49</v>
+      </c>
+      <c r="C142" s="8">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="7">
+        <v>16</v>
+      </c>
+      <c r="C143" s="8">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="7">
+        <v>35</v>
+      </c>
+      <c r="C144" s="8">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="7">
+        <v>126</v>
+      </c>
+      <c r="C145" s="8">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="7">
+        <v>127</v>
+      </c>
+      <c r="C146" s="8">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="7">
+        <v>135</v>
+      </c>
+      <c r="C147" s="8">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="7">
+        <v>59</v>
+      </c>
+      <c r="C148" s="8">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="7">
+        <v>106</v>
+      </c>
+      <c r="C149" s="8">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="7">
+        <v>49</v>
+      </c>
+      <c r="C150" s="8">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="7">
+        <v>38</v>
+      </c>
+      <c r="C151" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="7">
+        <v>16</v>
+      </c>
+      <c r="C152" s="8">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="7">
+        <v>43</v>
+      </c>
+      <c r="C153" s="8">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="7">
+        <v>273</v>
+      </c>
+      <c r="C154" s="8">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="7">
+        <v>43</v>
+      </c>
+      <c r="C155" s="8">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="7">
+        <v>35</v>
+      </c>
+      <c r="C156" s="8">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="7">
+        <v>43</v>
+      </c>
+      <c r="C157" s="8">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="7">
+        <v>42</v>
+      </c>
+      <c r="C158" s="8">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="7">
+        <v>32</v>
+      </c>
+      <c r="C159" s="8">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="7">
+        <v>56</v>
+      </c>
+      <c r="C160" s="8">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="7">
+        <v>313</v>
+      </c>
+      <c r="C161" s="8">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="7">
+        <v>311</v>
+      </c>
+      <c r="C162" s="8">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="7">
+        <v>176</v>
+      </c>
+      <c r="C163" s="8">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="7">
+        <v>53</v>
+      </c>
+      <c r="C164" s="8">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="7">
+        <v>242</v>
+      </c>
+      <c r="C165" s="8">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="7">
+        <v>366</v>
+      </c>
+      <c r="C166" s="8">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="7">
+        <v>246</v>
+      </c>
+      <c r="C167" s="8">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="7">
+        <v>313</v>
+      </c>
+      <c r="C168" s="8">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="7">
+        <v>227</v>
+      </c>
+      <c r="C169" s="8">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="7">
+        <v>312</v>
+      </c>
+      <c r="C170" s="8">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="7">
+        <v>312</v>
+      </c>
+      <c r="C171" s="8">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="7">
+        <v>312</v>
+      </c>
+      <c r="C172" s="8">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="7">
+        <v>88</v>
+      </c>
+      <c r="C173" s="8">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="7">
+        <v>111</v>
+      </c>
+      <c r="C174" s="8">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="7">
+        <v>254</v>
+      </c>
+      <c r="C175" s="8">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="7">
+        <v>252</v>
+      </c>
+      <c r="C176" s="8">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="7">
+        <v>296</v>
+      </c>
+      <c r="C177" s="8">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="7">
+        <v>469</v>
+      </c>
+      <c r="C178" s="8">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="7">
+        <v>117</v>
+      </c>
+      <c r="C179" s="8">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="7">
+        <v>117</v>
+      </c>
+      <c r="C180" s="8">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="7">
+        <v>468</v>
+      </c>
+      <c r="C181" s="8">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="7">
+        <v>362</v>
+      </c>
+      <c r="C182" s="8">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="7">
+        <v>313</v>
+      </c>
+      <c r="C183" s="8">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="7">
+        <v>71</v>
+      </c>
+      <c r="C184" s="8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="7">
+        <v>444</v>
+      </c>
+      <c r="C185" s="8">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="7">
+        <v>328</v>
+      </c>
+      <c r="C186" s="8">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="7">
+        <v>183</v>
+      </c>
+      <c r="C187" s="8">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="7">
+        <v>182</v>
+      </c>
+      <c r="C188" s="8">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="7">
+        <v>312</v>
+      </c>
+      <c r="C189" s="8">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="7">
+        <v>486</v>
+      </c>
+      <c r="C190" s="8">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="7">
+        <v>486</v>
+      </c>
+      <c r="C191" s="8">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="7">
+        <v>313</v>
+      </c>
+      <c r="C192" s="8">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="7">
+        <v>250</v>
+      </c>
+      <c r="C193" s="8">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="7">
+        <v>95</v>
+      </c>
+      <c r="C194" s="8">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="7">
+        <v>21</v>
+      </c>
+      <c r="C195" s="8">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="7">
+        <v>328</v>
+      </c>
+      <c r="C196" s="8">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" s="7">
+        <v>461</v>
+      </c>
+      <c r="C197" s="8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="7">
+        <v>95</v>
+      </c>
+      <c r="C198" s="8">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="7">
+        <v>19</v>
+      </c>
+      <c r="C199" s="8">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="7">
+        <v>95</v>
+      </c>
+      <c r="C200" s="8">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="7">
+        <v>33</v>
+      </c>
+      <c r="C201" s="8">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="7">
+        <v>59</v>
+      </c>
+      <c r="C202" s="8">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="7">
+        <v>218</v>
+      </c>
+      <c r="C203" s="8">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" s="7">
+        <v>417</v>
+      </c>
+      <c r="C204" s="8">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="7">
+        <v>196</v>
+      </c>
+      <c r="C205" s="8">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="7">
+        <v>195</v>
+      </c>
+      <c r="C206" s="8">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" s="7">
+        <v>407</v>
+      </c>
+      <c r="C207" s="8">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" s="7">
+        <v>126</v>
+      </c>
+      <c r="C208" s="8">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" s="7">
+        <v>127</v>
+      </c>
+      <c r="C209" s="8">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" s="7">
+        <v>429</v>
+      </c>
+      <c r="C210" s="8">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" s="7">
+        <v>429</v>
+      </c>
+      <c r="C211" s="8">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" s="7">
+        <v>120</v>
+      </c>
+      <c r="C212" s="8">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" s="7">
+        <v>120</v>
+      </c>
+      <c r="C213" s="8">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" s="7">
+        <v>135</v>
+      </c>
+      <c r="C214" s="8">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" s="7">
+        <v>49</v>
+      </c>
+      <c r="C215" s="8">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" s="7">
+        <v>384</v>
+      </c>
+      <c r="C216" s="8">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" s="7">
+        <v>49</v>
+      </c>
+      <c r="C217" s="8">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" s="7">
+        <v>59</v>
+      </c>
+      <c r="C218" s="8">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" s="7">
+        <v>14</v>
+      </c>
+      <c r="C219" s="8">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" s="7">
+        <v>10</v>
+      </c>
+      <c r="C220" s="8">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" s="7">
+        <v>311</v>
+      </c>
+      <c r="C221" s="8">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="7">
+        <v>10</v>
+      </c>
+      <c r="C222" s="8">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" s="7">
+        <v>209</v>
+      </c>
+      <c r="C223" s="8">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" s="7">
+        <v>10</v>
+      </c>
+      <c r="C224" s="8">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="7">
+        <v>314</v>
+      </c>
+      <c r="C225" s="8">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="7">
+        <v>19</v>
+      </c>
+      <c r="C226" s="8">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" s="7">
+        <v>314</v>
+      </c>
+      <c r="C227" s="8">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="7">
+        <v>35</v>
+      </c>
+      <c r="C228" s="8">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="7">
+        <v>313</v>
+      </c>
+      <c r="C229" s="8">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" s="7">
+        <v>135</v>
+      </c>
+      <c r="C230" s="8">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="7">
+        <v>164</v>
+      </c>
+      <c r="C231" s="8">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" s="7">
+        <v>145</v>
+      </c>
+      <c r="C232" s="8">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="7">
+        <v>145</v>
+      </c>
+      <c r="C233" s="8">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" s="7">
+        <v>487</v>
+      </c>
+      <c r="C234" s="8">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="7">
+        <v>196</v>
+      </c>
+      <c r="C235" s="8">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" s="7">
+        <v>195</v>
+      </c>
+      <c r="C236" s="8">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" s="7">
+        <v>16</v>
+      </c>
+      <c r="C237" s="8">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" s="7">
+        <v>38</v>
+      </c>
+      <c r="C238" s="8">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" s="7">
+        <v>104</v>
+      </c>
+      <c r="C239" s="8">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="7">
+        <v>54</v>
+      </c>
+      <c r="C240" s="8">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" s="7">
+        <v>328</v>
+      </c>
+      <c r="C241" s="8">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" s="7">
+        <v>328</v>
+      </c>
+      <c r="C242" s="8">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" s="7">
+        <v>439</v>
+      </c>
+      <c r="C243" s="8">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" s="7">
+        <v>33</v>
+      </c>
+      <c r="C244" s="8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" s="7">
+        <v>34</v>
+      </c>
+      <c r="C245" s="8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" s="7">
+        <v>56</v>
+      </c>
+      <c r="C246" s="8">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" s="7">
+        <v>16</v>
+      </c>
+      <c r="C247" s="8">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" s="7">
+        <v>43</v>
+      </c>
+      <c r="C248" s="8">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="7">
+        <v>120</v>
+      </c>
+      <c r="C249" s="8">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="7">
+        <v>44</v>
+      </c>
+      <c r="C250" s="8">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="7">
+        <v>36</v>
+      </c>
+      <c r="C251" s="8">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="7">
+        <v>43</v>
+      </c>
+      <c r="C252" s="8">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="7">
+        <v>238</v>
+      </c>
+      <c r="C253" s="8">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="7">
+        <v>42</v>
+      </c>
+      <c r="C254" s="8">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="7">
+        <v>38</v>
+      </c>
+      <c r="C255" s="8">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" s="7">
+        <v>38</v>
+      </c>
+      <c r="C256" s="8">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="7">
+        <v>38</v>
+      </c>
+      <c r="C257" s="8">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="7">
+        <v>328</v>
+      </c>
+      <c r="C258" s="8">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="7">
+        <v>328</v>
+      </c>
+      <c r="C259" s="8">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="7">
+        <v>312</v>
+      </c>
+      <c r="C260" s="8">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" s="7">
+        <v>312</v>
+      </c>
+      <c r="C261" s="8">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="7">
+        <v>312</v>
+      </c>
+      <c r="C262" s="8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="7">
+        <v>234</v>
+      </c>
+      <c r="C263" s="8">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="7">
+        <v>210</v>
+      </c>
+      <c r="C264" s="8">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="7">
+        <v>196</v>
+      </c>
+      <c r="C265" s="8">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="7">
+        <v>195</v>
+      </c>
+      <c r="C266" s="8">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="7">
+        <v>417</v>
+      </c>
+      <c r="C267" s="8">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="7">
+        <v>218</v>
+      </c>
+      <c r="C268" s="8">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" s="7">
+        <v>125</v>
+      </c>
+      <c r="C269" s="8">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" s="7">
+        <v>69</v>
+      </c>
+      <c r="C270" s="8">
+        <v>379</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -111,6 +111,9 @@
       <c r="B2" s="7">
         <v>145</v>
       </c>
+      <c r="C2" s="8">
+        <v>458</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="7">
@@ -122,7 +125,7 @@
     </row>
     <row r="4">
       <c r="B4" s="7">
-        <v>169</v>
+        <v>499</v>
       </c>
       <c r="C4" s="8">
         <v>404</v>
@@ -138,818 +141,818 @@
     </row>
     <row r="6">
       <c r="B6" s="7">
-        <v>54</v>
+        <v>260</v>
       </c>
       <c r="C6" s="8">
-        <v>32</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="7">
-        <v>260</v>
+        <v>11</v>
       </c>
       <c r="C7" s="8">
-        <v>296</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7">
-        <v>11</v>
+        <v>359</v>
       </c>
       <c r="C8" s="8">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7">
-        <v>359</v>
+        <v>428</v>
       </c>
       <c r="C9" s="8">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7">
-        <v>428</v>
+        <v>30</v>
       </c>
       <c r="C10" s="8">
-        <v>444</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C12" s="8">
-        <v>53</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="7">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C13" s="8">
-        <v>13</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C14" s="8">
-        <v>27</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C15" s="8">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C16" s="8">
-        <v>440</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C17" s="8">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="C18" s="8">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="C19" s="8">
-        <v>54</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7">
-        <v>2</v>
+        <v>444</v>
       </c>
       <c r="C20" s="8">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="7">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="C21" s="8">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="7">
-        <v>320</v>
+        <v>22</v>
       </c>
       <c r="C22" s="8">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="7">
-        <v>444</v>
+        <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="7">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="C24" s="8">
-        <v>450</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="7">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="C25" s="8">
-        <v>453</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="C26" s="8">
-        <v>453</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="7">
-        <v>215</v>
+        <v>314</v>
       </c>
       <c r="C27" s="8">
-        <v>322</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="7">
-        <v>214</v>
+        <v>450</v>
       </c>
       <c r="C28" s="8">
-        <v>320</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="7">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="C29" s="8">
-        <v>324</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7">
-        <v>314</v>
+        <v>177</v>
       </c>
       <c r="C30" s="8">
-        <v>454</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7">
-        <v>450</v>
+        <v>186</v>
       </c>
       <c r="C31" s="8">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="C32" s="8">
-        <v>454</v>
+        <v>480</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C33" s="8">
-        <v>245</v>
+        <v>480</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="C34" s="8">
-        <v>468</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="C35" s="8">
-        <v>480</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="7">
-        <v>165</v>
+        <v>323</v>
       </c>
       <c r="C36" s="8">
-        <v>480</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="C37" s="8">
-        <v>22</v>
+        <v>515</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="7">
-        <v>264</v>
+        <v>53</v>
       </c>
       <c r="C38" s="8">
-        <v>509</v>
+        <v>531</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="7">
-        <v>323</v>
+        <v>98</v>
       </c>
       <c r="C39" s="8">
-        <v>510</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="7">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C40" s="8">
-        <v>515</v>
+        <v>451</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="7">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="C41" s="8">
-        <v>531</v>
+        <v>451</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="7">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C42" s="8">
-        <v>534</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="7">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="C43" s="8">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="7">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="C44" s="8">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="7">
-        <v>59</v>
+        <v>209</v>
       </c>
       <c r="C45" s="8">
-        <v>451</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="7">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="C46" s="8">
-        <v>455</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="7">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="C47" s="8">
-        <v>455</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="7">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="C48" s="8">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C49" s="8">
-        <v>310</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="7">
-        <v>311</v>
+        <v>186</v>
       </c>
       <c r="C50" s="8">
-        <v>313</v>
+        <v>574</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C51" s="8">
-        <v>313</v>
+        <v>574</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="7">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="C52" s="8">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="C53" s="8">
-        <v>574</v>
+        <v>597</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C54" s="8">
-        <v>574</v>
+        <v>597</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="C55" s="8">
-        <v>574</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="7">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C56" s="8">
-        <v>597</v>
+        <v>618</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="C57" s="8">
-        <v>597</v>
+        <v>617</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="7">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="C58" s="8">
-        <v>463</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="C59" s="8">
-        <v>62</v>
+        <v>628</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="7">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="C60" s="8">
-        <v>618</v>
+        <v>628</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="7">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="C61" s="8">
-        <v>617</v>
+        <v>627</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="7">
-        <v>271</v>
+        <v>55</v>
       </c>
       <c r="C62" s="8">
-        <v>25</v>
+        <v>626</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C63" s="8">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="7">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="C64" s="8">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="7">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="C65" s="8">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C66" s="8">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="7">
-        <v>277</v>
+        <v>27</v>
       </c>
       <c r="C67" s="8">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="7">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="C68" s="8">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="7">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="C69" s="8">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="7">
-        <v>60</v>
+        <v>361</v>
       </c>
       <c r="C70" s="8">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="7">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="C71" s="8">
-        <v>622</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="7">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="C72" s="8">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="7">
-        <v>158</v>
+        <v>313</v>
       </c>
       <c r="C73" s="8">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="7">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="C74" s="8">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="7">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C75" s="8">
-        <v>100</v>
+        <v>613</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="7">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="C76" s="8">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="7">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="C77" s="8">
-        <v>614</v>
+        <v>607</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="7">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="C78" s="8">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="7">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="C79" s="8">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="7">
-        <v>236</v>
+        <v>55</v>
       </c>
       <c r="C80" s="8">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="7">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="C81" s="8">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="7">
-        <v>363</v>
+        <v>458</v>
       </c>
       <c r="C82" s="8">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="7">
-        <v>204</v>
+        <v>22</v>
       </c>
       <c r="C83" s="8">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="7">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="C84" s="8">
-        <v>605</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="7">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C85" s="8">
-        <v>605</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="7">
-        <v>458</v>
+        <v>226</v>
       </c>
       <c r="C86" s="8">
-        <v>604</v>
+        <v>366</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="7">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C87" s="8">
-        <v>604</v>
+        <v>652</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="7">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="C88" s="8">
-        <v>85</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="7">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="C89" s="8">
-        <v>37</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="7">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="C90" s="8">
-        <v>366</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="7">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="C91" s="8">
-        <v>652</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="7">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C92" s="8">
-        <v>149</v>
+        <v>462</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="7">
-        <v>309</v>
+        <v>117</v>
       </c>
       <c r="C93" s="8">
-        <v>149</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="7">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="C94" s="8">
-        <v>149</v>
+        <v>646</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="7">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="C95" s="8">
-        <v>107</v>
+        <v>646</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="7">
-        <v>20</v>
+        <v>480</v>
       </c>
       <c r="C96" s="8">
-        <v>462</v>
+        <v>587</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="7">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C97" s="8">
-        <v>14</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="7">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="C98" s="8">
-        <v>646</v>
+        <v>538</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="7">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C99" s="8">
-        <v>646</v>
+        <v>539</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="7">
-        <v>480</v>
+        <v>363</v>
       </c>
       <c r="C100" s="8">
-        <v>587</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="7">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C101" s="8">
-        <v>119</v>
+        <v>561</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="7">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C102" s="8">
-        <v>538</v>
+        <v>682</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="7">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C103" s="8">
-        <v>539</v>
+        <v>682</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="7">
-        <v>363</v>
+        <v>22</v>
       </c>
       <c r="C104" s="8">
-        <v>463</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="7">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C105" s="8">
-        <v>561</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="7">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C106" s="8">
-        <v>682</v>
+        <v>459</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="7">
-        <v>255</v>
+        <v>458</v>
       </c>
       <c r="C107" s="8">
-        <v>682</v>
+        <v>459</v>
       </c>
     </row>
     <row r="108">
@@ -957,15 +960,15 @@
         <v>22</v>
       </c>
       <c r="C108" s="8">
-        <v>15</v>
+        <v>479</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="7">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="C109" s="8">
-        <v>20</v>
+        <v>479</v>
       </c>
     </row>
     <row r="110">
@@ -973,15 +976,15 @@
         <v>22</v>
       </c>
       <c r="C110" s="8">
-        <v>459</v>
+        <v>509</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="7">
-        <v>458</v>
+        <v>264</v>
       </c>
       <c r="C111" s="8">
-        <v>459</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112">
@@ -989,39 +992,39 @@
         <v>22</v>
       </c>
       <c r="C112" s="8">
-        <v>479</v>
+        <v>575</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="7">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="C113" s="8">
-        <v>479</v>
+        <v>600</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C114" s="8">
-        <v>509</v>
+        <v>600</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="7">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="C115" s="8">
-        <v>20</v>
+        <v>642</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="7">
-        <v>22</v>
+        <v>264</v>
       </c>
       <c r="C116" s="8">
-        <v>575</v>
+        <v>642</v>
       </c>
     </row>
     <row r="117">
@@ -1029,47 +1032,47 @@
         <v>22</v>
       </c>
       <c r="C117" s="8">
-        <v>600</v>
+        <v>643</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="7">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C118" s="8">
-        <v>600</v>
+        <v>643</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="7">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="C119" s="8">
-        <v>642</v>
+        <v>274</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="7">
-        <v>264</v>
+        <v>145</v>
       </c>
       <c r="C120" s="8">
-        <v>642</v>
+        <v>276</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="7">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="C121" s="8">
-        <v>643</v>
+        <v>279</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="7">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="C122" s="8">
-        <v>643</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123">
@@ -1077,1183 +1080,2847 @@
         <v>145</v>
       </c>
       <c r="C123" s="8">
-        <v>274</v>
+        <v>603</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="7">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="C124" s="8">
-        <v>276</v>
+        <v>138</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="7">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="C125" s="8">
-        <v>279</v>
+        <v>241</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="7">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="C126" s="8">
-        <v>283</v>
+        <v>461</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="7">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="C127" s="8">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="7">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="C128" s="8">
-        <v>603</v>
+        <v>462</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" s="7">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C129" s="8">
-        <v>138</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="7">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C130" s="8">
-        <v>241</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="7">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="C131" s="8">
-        <v>461</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="7">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C132" s="8">
-        <v>462</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" s="7">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C133" s="8">
-        <v>462</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="7">
-        <v>56</v>
+        <v>485</v>
       </c>
       <c r="C134" s="8">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="7">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C135" s="8">
-        <v>28</v>
+        <v>131</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="7">
-        <v>248</v>
+        <v>135</v>
       </c>
       <c r="C136" s="8">
-        <v>35</v>
+        <v>131</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="7">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C137" s="8">
-        <v>36</v>
+        <v>131</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="7">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C138" s="8">
-        <v>40</v>
+        <v>233</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="7">
-        <v>485</v>
+        <v>35</v>
       </c>
       <c r="C139" s="8">
-        <v>52</v>
+        <v>233</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="7">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="C140" s="8">
-        <v>131</v>
+        <v>417</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="7">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C141" s="8">
-        <v>131</v>
+        <v>417</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="7">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="C142" s="8">
-        <v>131</v>
+        <v>436</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="7">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C143" s="8">
-        <v>233</v>
+        <v>436</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" s="7">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C144" s="8">
-        <v>233</v>
+        <v>519</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="7">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="C145" s="8">
-        <v>417</v>
+        <v>519</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="7">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="C146" s="8">
-        <v>417</v>
+        <v>524</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="7">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="C147" s="8">
-        <v>436</v>
+        <v>523</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" s="7">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C148" s="8">
-        <v>436</v>
+        <v>525</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="7">
-        <v>106</v>
+        <v>273</v>
       </c>
       <c r="C149" s="8">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="7">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C150" s="8">
-        <v>519</v>
+        <v>526</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="7">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C151" s="8">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="7">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C152" s="8">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C153" s="8">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="7">
-        <v>273</v>
+        <v>32</v>
       </c>
       <c r="C154" s="8">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="7">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C155" s="8">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7">
-        <v>35</v>
+        <v>313</v>
       </c>
       <c r="C156" s="8">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="7">
-        <v>43</v>
+        <v>311</v>
       </c>
       <c r="C157" s="8">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="C158" s="8">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C159" s="8">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7">
-        <v>56</v>
+        <v>242</v>
       </c>
       <c r="C160" s="8">
-        <v>530</v>
+        <v>554</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="C161" s="8">
-        <v>530</v>
+        <v>555</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="C162" s="8">
-        <v>532</v>
+        <v>555</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="7">
-        <v>176</v>
+        <v>313</v>
       </c>
       <c r="C163" s="8">
-        <v>533</v>
+        <v>556</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="7">
-        <v>53</v>
+        <v>227</v>
       </c>
       <c r="C164" s="8">
-        <v>533</v>
+        <v>556</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="7">
-        <v>242</v>
+        <v>312</v>
       </c>
       <c r="C165" s="8">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7">
-        <v>366</v>
+        <v>312</v>
       </c>
       <c r="C166" s="8">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="7">
-        <v>246</v>
+        <v>312</v>
       </c>
       <c r="C167" s="8">
-        <v>555</v>
+        <v>568</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="C168" s="8">
-        <v>556</v>
+        <v>569</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7">
-        <v>227</v>
+        <v>111</v>
       </c>
       <c r="C169" s="8">
-        <v>556</v>
+        <v>569</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7">
-        <v>312</v>
+        <v>254</v>
       </c>
       <c r="C170" s="8">
-        <v>557</v>
+        <v>570</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="7">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="C171" s="8">
-        <v>558</v>
+        <v>571</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="7">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C172" s="8">
-        <v>568</v>
+        <v>713</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="7">
-        <v>88</v>
+        <v>469</v>
       </c>
       <c r="C173" s="8">
-        <v>569</v>
+        <v>712</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="7">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C174" s="8">
-        <v>569</v>
+        <v>711</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7">
-        <v>254</v>
+        <v>117</v>
       </c>
       <c r="C175" s="8">
-        <v>570</v>
+        <v>710</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="7">
-        <v>252</v>
+        <v>468</v>
       </c>
       <c r="C176" s="8">
-        <v>571</v>
+        <v>709</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="7">
-        <v>296</v>
+        <v>362</v>
       </c>
       <c r="C177" s="8">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="7">
+        <v>313</v>
+      </c>
+      <c r="C178" s="8">
         <v>469</v>
-      </c>
-      <c r="C178" s="8">
-        <v>712</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="7">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="C179" s="8">
-        <v>711</v>
+        <v>44</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="7">
-        <v>117</v>
+        <v>444</v>
       </c>
       <c r="C180" s="8">
-        <v>710</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" s="7">
-        <v>468</v>
+        <v>328</v>
       </c>
       <c r="C181" s="8">
-        <v>709</v>
+        <v>516</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="7">
-        <v>362</v>
+        <v>183</v>
       </c>
       <c r="C182" s="8">
-        <v>708</v>
+        <v>518</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" s="7">
-        <v>313</v>
+        <v>182</v>
       </c>
       <c r="C183" s="8">
-        <v>469</v>
+        <v>518</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="7">
-        <v>71</v>
+        <v>312</v>
       </c>
       <c r="C184" s="8">
-        <v>44</v>
+        <v>521</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" s="7">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="C185" s="8">
-        <v>449</v>
+        <v>521</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" s="7">
-        <v>328</v>
+        <v>486</v>
       </c>
       <c r="C186" s="8">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" s="7">
-        <v>183</v>
+        <v>313</v>
       </c>
       <c r="C187" s="8">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="7">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="C188" s="8">
-        <v>518</v>
+        <v>572</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" s="7">
-        <v>312</v>
+        <v>95</v>
       </c>
       <c r="C189" s="8">
-        <v>521</v>
+        <v>572</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" s="7">
-        <v>486</v>
+        <v>21</v>
       </c>
       <c r="C190" s="8">
-        <v>521</v>
+        <v>573</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" s="7">
-        <v>486</v>
+        <v>328</v>
       </c>
       <c r="C191" s="8">
-        <v>522</v>
+        <v>573</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" s="7">
-        <v>313</v>
+        <v>461</v>
       </c>
       <c r="C192" s="8">
-        <v>522</v>
+        <v>576</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" s="7">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="C193" s="8">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" s="7">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="C194" s="8">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" s="7">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="C195" s="8">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="196">
       <c r="B196" s="7">
-        <v>328</v>
+        <v>33</v>
       </c>
       <c r="C196" s="8">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" s="7">
-        <v>461</v>
+        <v>59</v>
       </c>
       <c r="C197" s="8">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" s="7">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="C198" s="8">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" s="7">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="C199" s="8">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="7">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="C200" s="8">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" s="7">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="C201" s="8">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" s="7">
-        <v>59</v>
+        <v>407</v>
       </c>
       <c r="C202" s="8">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" s="7">
-        <v>218</v>
+        <v>126</v>
       </c>
       <c r="C203" s="8">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" s="7">
-        <v>417</v>
+        <v>127</v>
       </c>
       <c r="C204" s="8">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" s="7">
-        <v>196</v>
+        <v>429</v>
       </c>
       <c r="C205" s="8">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="7">
-        <v>195</v>
+        <v>429</v>
       </c>
       <c r="C206" s="8">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="7">
-        <v>407</v>
+        <v>120</v>
       </c>
       <c r="C207" s="8">
-        <v>582</v>
+        <v>593</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" s="7">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C208" s="8">
-        <v>583</v>
+        <v>594</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="7">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C209" s="8">
-        <v>583</v>
+        <v>595</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" s="7">
-        <v>429</v>
+        <v>49</v>
       </c>
       <c r="C210" s="8">
-        <v>584</v>
+        <v>595</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="7">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="C211" s="8">
-        <v>586</v>
+        <v>596</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" s="7">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="C212" s="8">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" s="7">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="C213" s="8">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="7">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="C214" s="8">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" s="7">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C215" s="8">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="7">
-        <v>384</v>
+        <v>311</v>
       </c>
       <c r="C216" s="8">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" s="7">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C217" s="8">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="7">
-        <v>59</v>
+        <v>209</v>
       </c>
       <c r="C218" s="8">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C219" s="8">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" s="7">
-        <v>10</v>
+        <v>314</v>
       </c>
       <c r="C220" s="8">
-        <v>599</v>
+        <v>609</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" s="7">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="C221" s="8">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="7">
-        <v>10</v>
+        <v>314</v>
       </c>
       <c r="C222" s="8">
-        <v>601</v>
+        <v>610</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="7">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="C223" s="8">
-        <v>602</v>
+        <v>610</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="7">
-        <v>10</v>
+        <v>313</v>
       </c>
       <c r="C224" s="8">
-        <v>602</v>
+        <v>611</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" s="7">
-        <v>314</v>
+        <v>135</v>
       </c>
       <c r="C225" s="8">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="7">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="C226" s="8">
-        <v>609</v>
+        <v>629</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="7">
-        <v>314</v>
+        <v>145</v>
       </c>
       <c r="C227" s="8">
-        <v>610</v>
+        <v>630</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="7">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="C228" s="8">
-        <v>610</v>
+        <v>631</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="7">
-        <v>313</v>
+        <v>487</v>
       </c>
       <c r="C229" s="8">
-        <v>611</v>
+        <v>633</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="7">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="C230" s="8">
-        <v>612</v>
+        <v>260</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="7">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="C231" s="8">
-        <v>629</v>
+        <v>260</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="7">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="C232" s="8">
-        <v>630</v>
+        <v>264</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="7">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="C233" s="8">
-        <v>631</v>
+        <v>264</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" s="7">
-        <v>487</v>
+        <v>104</v>
       </c>
       <c r="C234" s="8">
-        <v>633</v>
+        <v>272</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="7">
-        <v>196</v>
+        <v>54</v>
       </c>
       <c r="C235" s="8">
-        <v>260</v>
+        <v>294</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="7">
-        <v>195</v>
+        <v>328</v>
       </c>
       <c r="C236" s="8">
-        <v>260</v>
+        <v>296</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="7">
-        <v>16</v>
+        <v>328</v>
       </c>
       <c r="C237" s="8">
-        <v>264</v>
+        <v>299</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="7">
-        <v>38</v>
+        <v>439</v>
       </c>
       <c r="C238" s="8">
-        <v>264</v>
+        <v>301</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="7">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="C239" s="8">
-        <v>272</v>
+        <v>307</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="7">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C240" s="8">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="7">
-        <v>328</v>
+        <v>56</v>
       </c>
       <c r="C241" s="8">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="7">
-        <v>328</v>
+        <v>16</v>
       </c>
       <c r="C242" s="8">
-        <v>299</v>
+        <v>316</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="7">
-        <v>439</v>
+        <v>43</v>
       </c>
       <c r="C243" s="8">
-        <v>301</v>
+        <v>326</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="7">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="C244" s="8">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="7">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C245" s="8">
-        <v>307</v>
+        <v>330</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="7">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C246" s="8">
-        <v>308</v>
+        <v>332</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="7">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C247" s="8">
-        <v>316</v>
+        <v>334</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="7">
-        <v>43</v>
+        <v>238</v>
       </c>
       <c r="C248" s="8">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="7">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="C249" s="8">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="7">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C250" s="8">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C251" s="8">
-        <v>332</v>
+        <v>347</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="7">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C252" s="8">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" s="7">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C253" s="8">
-        <v>336</v>
+        <v>353</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="7">
-        <v>42</v>
+        <v>328</v>
       </c>
       <c r="C254" s="8">
-        <v>338</v>
+        <v>354</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" s="7">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="C255" s="8">
-        <v>344</v>
+        <v>358</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="7">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="C256" s="8">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="7">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="C257" s="8">
-        <v>349</v>
+        <v>363</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="7">
-        <v>328</v>
+        <v>234</v>
       </c>
       <c r="C258" s="8">
-        <v>353</v>
+        <v>368</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="7">
-        <v>328</v>
+        <v>210</v>
       </c>
       <c r="C259" s="8">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="7">
-        <v>312</v>
+        <v>196</v>
       </c>
       <c r="C260" s="8">
-        <v>358</v>
+        <v>374</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="7">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="C261" s="8">
-        <v>361</v>
+        <v>375</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="7">
-        <v>312</v>
+        <v>417</v>
       </c>
       <c r="C262" s="8">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="7">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C263" s="8">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="7">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C264" s="8">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="7">
-        <v>196</v>
+        <v>69</v>
       </c>
       <c r="C265" s="8">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="7">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="C266" s="8">
-        <v>375</v>
+        <v>225</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="7">
-        <v>417</v>
+        <v>368</v>
       </c>
       <c r="C267" s="8">
-        <v>378</v>
+        <v>115</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="7">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="C268" s="8">
-        <v>378</v>
+        <v>673</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="7">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="C269" s="8">
-        <v>379</v>
+        <v>674</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="7">
+        <v>444</v>
+      </c>
+      <c r="C270" s="8">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" s="7">
+        <v>485</v>
+      </c>
+      <c r="C271" s="8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="7">
+        <v>311</v>
+      </c>
+      <c r="C272" s="8">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="7">
+        <v>50</v>
+      </c>
+      <c r="C273" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="7">
+        <v>110</v>
+      </c>
+      <c r="C274" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="7">
+        <v>111</v>
+      </c>
+      <c r="C275" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" s="7">
+        <v>113</v>
+      </c>
+      <c r="C276" s="8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" s="7">
+        <v>137</v>
+      </c>
+      <c r="C277" s="8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="7">
+        <v>49</v>
+      </c>
+      <c r="C278" s="8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" s="7">
+        <v>59</v>
+      </c>
+      <c r="C279" s="8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" s="7">
+        <v>59</v>
+      </c>
+      <c r="C280" s="8">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="7">
+        <v>26</v>
+      </c>
+      <c r="C281" s="8">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="7">
+        <v>271</v>
+      </c>
+      <c r="C282" s="8">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" s="7">
+        <v>126</v>
+      </c>
+      <c r="C283" s="8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" s="7">
+        <v>127</v>
+      </c>
+      <c r="C284" s="8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" s="7">
+        <v>120</v>
+      </c>
+      <c r="C285" s="8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" s="7">
+        <v>129</v>
+      </c>
+      <c r="C286" s="8">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="7">
+        <v>132</v>
+      </c>
+      <c r="C287" s="8">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="7">
+        <v>139</v>
+      </c>
+      <c r="C288" s="8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" s="7">
+        <v>149</v>
+      </c>
+      <c r="C289" s="8">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" s="7">
+        <v>164</v>
+      </c>
+      <c r="C290" s="8">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="7">
+        <v>166</v>
+      </c>
+      <c r="C291" s="8">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="7">
+        <v>55</v>
+      </c>
+      <c r="C292" s="8">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="7">
+        <v>445</v>
+      </c>
+      <c r="C293" s="8">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="7">
+        <v>167</v>
+      </c>
+      <c r="C294" s="8">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" s="7">
+        <v>220</v>
+      </c>
+      <c r="C295" s="8">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" s="7">
+        <v>128</v>
+      </c>
+      <c r="C296" s="8">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" s="7">
+        <v>245</v>
+      </c>
+      <c r="C297" s="8">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="7">
+        <v>38</v>
+      </c>
+      <c r="C298" s="8">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="7">
+        <v>522</v>
+      </c>
+      <c r="C299" s="8">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" s="7">
+        <v>522</v>
+      </c>
+      <c r="C300" s="8">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" s="7">
+        <v>201</v>
+      </c>
+      <c r="C301" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="7">
+        <v>200</v>
+      </c>
+      <c r="C302" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="7">
+        <v>204</v>
+      </c>
+      <c r="C303" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" s="7">
+        <v>251</v>
+      </c>
+      <c r="C304" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="7">
+        <v>209</v>
+      </c>
+      <c r="C305" s="8">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="7">
+        <v>206</v>
+      </c>
+      <c r="C306" s="8">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="7">
+        <v>209</v>
+      </c>
+      <c r="C307" s="8">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" s="7">
+        <v>209</v>
+      </c>
+      <c r="C308" s="8">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" s="7">
+        <v>313</v>
+      </c>
+      <c r="C309" s="8">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="7">
+        <v>36</v>
+      </c>
+      <c r="C310" s="8">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="7">
+        <v>35</v>
+      </c>
+      <c r="C311" s="8">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="7">
+        <v>53</v>
+      </c>
+      <c r="C312" s="8">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="7">
+        <v>53</v>
+      </c>
+      <c r="C313" s="8">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="7">
+        <v>53</v>
+      </c>
+      <c r="C314" s="8">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="7">
+        <v>40</v>
+      </c>
+      <c r="C315" s="8">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="7">
+        <v>39</v>
+      </c>
+      <c r="C316" s="8">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" s="7">
+        <v>123</v>
+      </c>
+      <c r="C317" s="8">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" s="7">
+        <v>123</v>
+      </c>
+      <c r="C318" s="8">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="7">
+        <v>384</v>
+      </c>
+      <c r="C319" s="8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="7">
+        <v>185</v>
+      </c>
+      <c r="C320" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="7">
+        <v>125</v>
+      </c>
+      <c r="C321" s="8">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="7">
         <v>69</v>
       </c>
-      <c r="C270" s="8">
-        <v>379</v>
+      <c r="C322" s="8">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" s="7">
+        <v>106</v>
+      </c>
+      <c r="C323" s="8">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="7">
+        <v>69</v>
+      </c>
+      <c r="C324" s="8">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" s="7">
+        <v>106</v>
+      </c>
+      <c r="C325" s="8">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" s="7">
+        <v>69</v>
+      </c>
+      <c r="C326" s="8">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" s="7">
+        <v>49</v>
+      </c>
+      <c r="C327" s="8">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" s="7">
+        <v>69</v>
+      </c>
+      <c r="C328" s="8">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="7">
+        <v>49</v>
+      </c>
+      <c r="C329" s="8">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="7">
+        <v>69</v>
+      </c>
+      <c r="C330" s="8">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" s="7">
+        <v>79</v>
+      </c>
+      <c r="C331" s="8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" s="7">
+        <v>19</v>
+      </c>
+      <c r="C332" s="8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" s="7">
+        <v>136</v>
+      </c>
+      <c r="C333" s="8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="7">
+        <v>100</v>
+      </c>
+      <c r="C334" s="8">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" s="7">
+        <v>123</v>
+      </c>
+      <c r="C335" s="8">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" s="7">
+        <v>119</v>
+      </c>
+      <c r="C336" s="8">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" s="7">
+        <v>429</v>
+      </c>
+      <c r="C337" s="8">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="7">
+        <v>489</v>
+      </c>
+      <c r="C338" s="8">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" s="7">
+        <v>27</v>
+      </c>
+      <c r="C339" s="8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" s="7">
+        <v>323</v>
+      </c>
+      <c r="C340" s="8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" s="7">
+        <v>324</v>
+      </c>
+      <c r="C341" s="8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" s="7">
+        <v>271</v>
+      </c>
+      <c r="C342" s="8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" s="7">
+        <v>59</v>
+      </c>
+      <c r="C343" s="8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" s="7">
+        <v>220</v>
+      </c>
+      <c r="C344" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" s="7">
+        <v>221</v>
+      </c>
+      <c r="C345" s="8">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" s="7">
+        <v>120</v>
+      </c>
+      <c r="C346" s="8">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" s="7">
+        <v>163</v>
+      </c>
+      <c r="C347" s="8">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" s="7">
+        <v>89</v>
+      </c>
+      <c r="C348" s="8">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" s="7">
+        <v>163</v>
+      </c>
+      <c r="C349" s="8">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="7">
+        <v>328</v>
+      </c>
+      <c r="C350" s="8">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" s="7">
+        <v>88</v>
+      </c>
+      <c r="C351" s="8">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" s="7">
+        <v>338</v>
+      </c>
+      <c r="C352" s="8">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" s="7">
+        <v>163</v>
+      </c>
+      <c r="C353" s="8">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" s="7">
+        <v>248</v>
+      </c>
+      <c r="C354" s="8">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" s="7">
+        <v>53</v>
+      </c>
+      <c r="C355" s="8">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" s="7">
+        <v>247</v>
+      </c>
+      <c r="C356" s="8">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" s="7">
+        <v>38</v>
+      </c>
+      <c r="C357" s="8">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="7">
+        <v>247</v>
+      </c>
+      <c r="C358" s="8">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="7">
+        <v>328</v>
+      </c>
+      <c r="C359" s="8">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="7">
+        <v>35</v>
+      </c>
+      <c r="C360" s="8">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="7">
+        <v>384</v>
+      </c>
+      <c r="C361" s="8">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="7">
+        <v>312</v>
+      </c>
+      <c r="C362" s="8">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" s="7">
+        <v>59</v>
+      </c>
+      <c r="C363" s="8">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" s="7">
+        <v>183</v>
+      </c>
+      <c r="C364" s="8">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" s="7">
+        <v>181</v>
+      </c>
+      <c r="C365" s="8">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="7">
+        <v>123</v>
+      </c>
+      <c r="C366" s="8">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="7">
+        <v>59</v>
+      </c>
+      <c r="C367" s="8">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" s="7">
+        <v>123</v>
+      </c>
+      <c r="C368" s="8">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" s="7">
+        <v>123</v>
+      </c>
+      <c r="C369" s="8">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" s="7">
+        <v>18</v>
+      </c>
+      <c r="C370" s="8">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" s="7">
+        <v>123</v>
+      </c>
+      <c r="C371" s="8">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" s="7">
+        <v>99</v>
+      </c>
+      <c r="C372" s="8">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" s="7">
+        <v>99</v>
+      </c>
+      <c r="C373" s="8">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="7">
+        <v>123</v>
+      </c>
+      <c r="C374" s="8">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" s="7">
+        <v>105</v>
+      </c>
+      <c r="C375" s="8">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" s="7">
+        <v>123</v>
+      </c>
+      <c r="C376" s="8">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" s="7">
+        <v>105</v>
+      </c>
+      <c r="C377" s="8">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="7">
+        <v>120</v>
+      </c>
+      <c r="C378" s="8">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="7">
+        <v>339</v>
+      </c>
+      <c r="C379" s="8">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="7">
+        <v>158</v>
+      </c>
+      <c r="C380" s="8">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="7">
+        <v>64</v>
+      </c>
+      <c r="C381" s="8">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="7">
+        <v>179</v>
+      </c>
+      <c r="C382" s="8">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="7">
+        <v>274</v>
+      </c>
+      <c r="C383" s="8">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" s="7">
+        <v>64</v>
+      </c>
+      <c r="C384" s="8">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" s="7">
+        <v>120</v>
+      </c>
+      <c r="C385" s="8">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="7">
+        <v>459</v>
+      </c>
+      <c r="C386" s="8">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="7">
+        <v>231</v>
+      </c>
+      <c r="C387" s="8">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" s="7">
+        <v>127</v>
+      </c>
+      <c r="C388" s="8">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" s="7">
+        <v>231</v>
+      </c>
+      <c r="C389" s="8">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="7">
+        <v>126</v>
+      </c>
+      <c r="C390" s="8">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" s="7">
+        <v>231</v>
+      </c>
+      <c r="C391" s="8">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" s="7">
+        <v>286</v>
+      </c>
+      <c r="C392" s="8">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="7">
+        <v>59</v>
+      </c>
+      <c r="C393" s="8">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" s="7">
+        <v>274</v>
+      </c>
+      <c r="C394" s="8">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" s="7">
+        <v>229</v>
+      </c>
+      <c r="C395" s="8">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="7">
+        <v>59</v>
+      </c>
+      <c r="C396" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="7">
+        <v>65</v>
+      </c>
+      <c r="C397" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" s="7">
+        <v>48</v>
+      </c>
+      <c r="C398" s="8">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="7">
+        <v>90</v>
+      </c>
+      <c r="C399" s="8">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="7">
+        <v>60</v>
+      </c>
+      <c r="C400" s="8">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="7">
+        <v>60</v>
+      </c>
+      <c r="C401" s="8">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="7">
+        <v>523</v>
+      </c>
+      <c r="C402" s="8">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" s="7">
+        <v>501</v>
+      </c>
+      <c r="C403" s="8">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="7">
+        <v>169</v>
+      </c>
+      <c r="C404" s="8">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" s="7">
+        <v>59</v>
+      </c>
+      <c r="C405" s="8">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" s="7">
+        <v>10</v>
+      </c>
+      <c r="C406" s="8">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="7">
+        <v>177</v>
+      </c>
+      <c r="C407" s="8">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" s="7">
+        <v>524</v>
+      </c>
+      <c r="C408" s="8">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" s="7">
+        <v>37</v>
+      </c>
+      <c r="C409" s="8">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="7">
+        <v>23</v>
+      </c>
+      <c r="C410" s="8">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" s="7">
+        <v>50</v>
+      </c>
+      <c r="C411" s="8">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" s="7">
+        <v>209</v>
+      </c>
+      <c r="C412" s="8">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="7">
+        <v>23</v>
+      </c>
+      <c r="C413" s="8">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="7">
+        <v>16</v>
+      </c>
+      <c r="C414" s="8">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" s="7">
+        <v>164</v>
+      </c>
+      <c r="C415" s="8">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" s="7">
+        <v>166</v>
+      </c>
+      <c r="C416" s="8">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" s="7">
+        <v>445</v>
+      </c>
+      <c r="C417" s="8">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" s="7">
+        <v>55</v>
+      </c>
+      <c r="C418" s="8">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" s="7">
+        <v>525</v>
+      </c>
+      <c r="C419" s="8">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" s="7">
+        <v>55</v>
+      </c>
+      <c r="C420" s="8">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" s="7">
+        <v>60</v>
+      </c>
+      <c r="C421" s="8">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" s="7">
+        <v>231</v>
+      </c>
+      <c r="C422" s="8">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" s="7">
+        <v>97</v>
+      </c>
+      <c r="C423" s="8">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" s="7">
+        <v>60</v>
+      </c>
+      <c r="C424" s="8">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" s="7">
+        <v>459</v>
+      </c>
+      <c r="C425" s="8">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" s="7">
+        <v>244</v>
+      </c>
+      <c r="C426" s="8">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" s="7">
+        <v>16</v>
+      </c>
+      <c r="C427" s="8">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" s="7">
+        <v>204</v>
+      </c>
+      <c r="C428" s="8">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" s="7">
+        <v>363</v>
+      </c>
+      <c r="C429" s="8">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" s="7">
+        <v>59</v>
+      </c>
+      <c r="C430" s="8">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" s="7">
+        <v>328</v>
+      </c>
+      <c r="C431" s="8">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" s="7">
+        <v>183</v>
+      </c>
+      <c r="C432" s="8">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" s="7">
+        <v>328</v>
+      </c>
+      <c r="C433" s="8">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" s="7">
+        <v>182</v>
+      </c>
+      <c r="C434" s="8">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" s="7">
+        <v>152</v>
+      </c>
+      <c r="C435" s="8">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" s="7">
+        <v>54</v>
+      </c>
+      <c r="C436" s="8">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" s="7">
+        <v>152</v>
+      </c>
+      <c r="C437" s="8">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" s="7">
+        <v>152</v>
+      </c>
+      <c r="C438" s="8">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" s="7">
+        <v>57</v>
+      </c>
+      <c r="C439" s="8">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" s="7">
+        <v>22</v>
+      </c>
+      <c r="C440" s="8">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" s="7">
+        <v>22</v>
+      </c>
+      <c r="C441" s="8">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" s="7">
+        <v>22</v>
+      </c>
+      <c r="C442" s="8">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" s="7">
+        <v>22</v>
+      </c>
+      <c r="C443" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" s="7">
+        <v>227</v>
+      </c>
+      <c r="C444" s="8">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" s="7">
+        <v>226</v>
+      </c>
+      <c r="C445" s="8">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" s="7">
+        <v>234</v>
+      </c>
+      <c r="C446" s="8">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" s="7">
+        <v>23</v>
+      </c>
+      <c r="C447" s="8">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" s="7">
+        <v>22</v>
+      </c>
+      <c r="C448" s="8">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" s="7">
+        <v>23</v>
+      </c>
+      <c r="C449" s="8">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" s="7">
+        <v>22</v>
+      </c>
+      <c r="C450" s="8">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" s="7">
+        <v>22</v>
+      </c>
+      <c r="C451" s="8">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" s="7">
+        <v>23</v>
+      </c>
+      <c r="C452" s="8">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" s="7">
+        <v>22</v>
+      </c>
+      <c r="C453" s="8">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" s="7">
+        <v>23</v>
+      </c>
+      <c r="C454" s="8">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" s="7">
+        <v>209</v>
+      </c>
+      <c r="C455" s="8">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" s="7">
+        <v>23</v>
+      </c>
+      <c r="C456" s="8">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" s="7">
+        <v>209</v>
+      </c>
+      <c r="C457" s="8">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" s="7">
+        <v>23</v>
+      </c>
+      <c r="C458" s="8">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="7">
+        <v>16</v>
+      </c>
+      <c r="C459" s="8">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" s="7">
+        <v>209</v>
+      </c>
+      <c r="C460" s="8">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" s="7">
+        <v>23</v>
+      </c>
+      <c r="C461" s="8">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" s="7">
+        <v>359</v>
+      </c>
+      <c r="C462" s="8">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" s="7">
+        <v>98</v>
+      </c>
+      <c r="C463" s="8">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" s="7">
+        <v>313</v>
+      </c>
+      <c r="C464" s="8">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" s="7">
+        <v>359</v>
+      </c>
+      <c r="C465" s="8">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" s="7">
+        <v>313</v>
+      </c>
+      <c r="C466" s="8">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" s="7">
+        <v>214</v>
+      </c>
+      <c r="C467" s="8">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" s="7">
+        <v>216</v>
+      </c>
+      <c r="C468" s="8">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" s="7">
+        <v>311</v>
+      </c>
+      <c r="C469" s="8">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" s="7">
+        <v>311</v>
+      </c>
+      <c r="C470" s="8">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" s="7">
+        <v>311</v>
+      </c>
+      <c r="C471" s="8">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" s="7">
+        <v>311</v>
+      </c>
+      <c r="C472" s="8">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" s="7">
+        <v>22</v>
+      </c>
+      <c r="C473" s="8">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" s="7">
+        <v>22</v>
+      </c>
+      <c r="C474" s="8">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" s="7">
+        <v>22</v>
+      </c>
+      <c r="C475" s="8">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" s="7">
+        <v>48</v>
+      </c>
+      <c r="C476" s="8">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" s="7">
+        <v>22</v>
+      </c>
+      <c r="C477" s="8">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" s="7">
+        <v>328</v>
+      </c>
+      <c r="C478" s="8">
+        <v>725</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -173,23 +173,23 @@
     </row>
     <row r="10">
       <c r="B10" s="7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="8">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="7">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
-        <v>53</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C12" s="8">
         <v>440</v>
@@ -197,15 +197,15 @@
     </row>
     <row r="13">
       <c r="B13" s="7">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="C13" s="8">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="8">
         <v>441</v>
@@ -213,23 +213,23 @@
     </row>
     <row r="15">
       <c r="B15" s="7">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C15" s="8">
-        <v>441</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C16" s="8">
-        <v>54</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="C17" s="8">
         <v>448</v>
@@ -237,7 +237,7 @@
     </row>
     <row r="18">
       <c r="B18" s="7">
-        <v>178</v>
+        <v>320</v>
       </c>
       <c r="C18" s="8">
         <v>448</v>
@@ -245,15 +245,15 @@
     </row>
     <row r="19">
       <c r="B19" s="7">
-        <v>320</v>
+        <v>444</v>
       </c>
       <c r="C19" s="8">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7">
-        <v>444</v>
+        <v>59</v>
       </c>
       <c r="C20" s="8">
         <v>450</v>
@@ -261,15 +261,15 @@
     </row>
     <row r="21">
       <c r="B21" s="7">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="C21" s="8">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C22" s="8">
         <v>453</v>
@@ -277,39 +277,39 @@
     </row>
     <row r="23">
       <c r="B23" s="7">
-        <v>10</v>
+        <v>215</v>
       </c>
       <c r="C23" s="8">
-        <v>453</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C24" s="8">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C25" s="8">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="C26" s="8">
-        <v>324</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="7">
-        <v>314</v>
+        <v>450</v>
       </c>
       <c r="C27" s="8">
         <v>454</v>
@@ -317,7 +317,7 @@
     </row>
     <row r="28">
       <c r="B28" s="7">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="C28" s="8">
         <v>454</v>
@@ -325,31 +325,31 @@
     </row>
     <row r="29">
       <c r="B29" s="7">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="C29" s="8">
-        <v>454</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C30" s="8">
-        <v>245</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="C31" s="8">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="8">
         <v>480</v>
@@ -357,63 +357,63 @@
     </row>
     <row r="33">
       <c r="B33" s="7">
-        <v>165</v>
+        <v>263</v>
       </c>
       <c r="C33" s="8">
-        <v>480</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C34" s="8">
-        <v>22</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="C35" s="8">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="7">
-        <v>323</v>
+        <v>163</v>
       </c>
       <c r="C36" s="8">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C37" s="8">
-        <v>515</v>
+        <v>531</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="7">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="C38" s="8">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="7">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C39" s="8">
-        <v>534</v>
+        <v>451</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C40" s="8">
         <v>451</v>
@@ -421,7 +421,7 @@
     </row>
     <row r="41">
       <c r="B41" s="7">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="C41" s="8">
         <v>451</v>
@@ -429,15 +429,15 @@
     </row>
     <row r="42">
       <c r="B42" s="7">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="C42" s="8">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="7">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="C43" s="8">
         <v>455</v>
@@ -445,15 +445,15 @@
     </row>
     <row r="44">
       <c r="B44" s="7">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="C44" s="8">
-        <v>455</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="7">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="C45" s="8">
         <v>310</v>
@@ -461,15 +461,15 @@
     </row>
     <row r="46">
       <c r="B46" s="7">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="C46" s="8">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="7">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="C47" s="8">
         <v>313</v>
@@ -477,23 +477,23 @@
     </row>
     <row r="48">
       <c r="B48" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C48" s="8">
-        <v>313</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="7">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="C49" s="8">
-        <v>56</v>
+        <v>574</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="7">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="C50" s="8">
         <v>574</v>
@@ -501,303 +501,303 @@
     </row>
     <row r="51">
       <c r="B51" s="7">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="C51" s="8">
-        <v>574</v>
+        <v>597</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="7">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="C52" s="8">
-        <v>15</v>
+        <v>597</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="C53" s="8">
-        <v>597</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="7">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="C54" s="8">
-        <v>597</v>
+        <v>618</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C55" s="8">
-        <v>463</v>
+        <v>617</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="7">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="C56" s="8">
-        <v>618</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="C57" s="8">
-        <v>617</v>
+        <v>628</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="7">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="C58" s="8">
-        <v>25</v>
+        <v>628</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="C59" s="8">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="7">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="C60" s="8">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="7">
-        <v>163</v>
+        <v>277</v>
       </c>
       <c r="C61" s="8">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="7">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="C62" s="8">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="7">
-        <v>277</v>
+        <v>60</v>
       </c>
       <c r="C63" s="8">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="7">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="C64" s="8">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="7">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C65" s="8">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="7">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="C66" s="8">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="7">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="C67" s="8">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="7">
-        <v>169</v>
+        <v>361</v>
       </c>
       <c r="C68" s="8">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="7">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="C69" s="8">
-        <v>619</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="7">
-        <v>361</v>
+        <v>69</v>
       </c>
       <c r="C70" s="8">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="7">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="C71" s="8">
-        <v>100</v>
+        <v>614</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="7">
-        <v>69</v>
+        <v>313</v>
       </c>
       <c r="C72" s="8">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="7">
-        <v>313</v>
+        <v>59</v>
       </c>
       <c r="C73" s="8">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="7">
-        <v>313</v>
+        <v>236</v>
       </c>
       <c r="C74" s="8">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="7">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C75" s="8">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="7">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="C76" s="8">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="7">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="C77" s="8">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="7">
-        <v>363</v>
+        <v>55</v>
       </c>
       <c r="C78" s="8">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="7">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="C79" s="8">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="7">
-        <v>55</v>
+        <v>458</v>
       </c>
       <c r="C80" s="8">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="7">
-        <v>255</v>
+        <v>22</v>
       </c>
       <c r="C81" s="8">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="7">
-        <v>458</v>
+        <v>104</v>
       </c>
       <c r="C82" s="8">
-        <v>604</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="7">
-        <v>22</v>
+        <v>248</v>
       </c>
       <c r="C83" s="8">
-        <v>604</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="7">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="C84" s="8">
-        <v>85</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="7">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="C85" s="8">
-        <v>37</v>
+        <v>652</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="7">
-        <v>226</v>
+        <v>46</v>
       </c>
       <c r="C86" s="8">
-        <v>366</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="7">
-        <v>60</v>
+        <v>309</v>
       </c>
       <c r="C87" s="8">
-        <v>652</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C88" s="8">
         <v>149</v>
@@ -805,66 +805,66 @@
     </row>
     <row r="89">
       <c r="B89" s="7">
-        <v>309</v>
+        <v>121</v>
       </c>
       <c r="C89" s="8">
-        <v>149</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="7">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C90" s="8">
-        <v>149</v>
+        <v>462</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="7">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C91" s="8">
-        <v>107</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="7">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="C92" s="8">
-        <v>462</v>
+        <v>646</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="7">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="C93" s="8">
-        <v>14</v>
+        <v>646</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="7">
-        <v>182</v>
+        <v>480</v>
       </c>
       <c r="C94" s="8">
-        <v>646</v>
+        <v>587</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="7">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C95" s="8">
-        <v>646</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="7">
-        <v>480</v>
+        <v>140</v>
       </c>
       <c r="C96" s="8">
-        <v>587</v>
+        <v>538</v>
       </c>
     </row>
     <row r="97">
@@ -872,55 +872,55 @@
         <v>140</v>
       </c>
       <c r="C97" s="8">
-        <v>119</v>
+        <v>539</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="7">
-        <v>140</v>
+        <v>363</v>
       </c>
       <c r="C98" s="8">
-        <v>538</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="7">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C99" s="8">
-        <v>539</v>
+        <v>561</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="7">
-        <v>363</v>
+        <v>55</v>
       </c>
       <c r="C100" s="8">
-        <v>463</v>
+        <v>682</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="7">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C101" s="8">
-        <v>561</v>
+        <v>682</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="7">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C102" s="8">
-        <v>682</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="7">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="C103" s="8">
-        <v>682</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104">
@@ -928,15 +928,15 @@
         <v>22</v>
       </c>
       <c r="C104" s="8">
-        <v>15</v>
+        <v>459</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="7">
-        <v>22</v>
+        <v>458</v>
       </c>
       <c r="C105" s="8">
-        <v>20</v>
+        <v>459</v>
       </c>
     </row>
     <row r="106">
@@ -944,15 +944,15 @@
         <v>22</v>
       </c>
       <c r="C106" s="8">
-        <v>459</v>
+        <v>479</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="7">
-        <v>458</v>
+        <v>166</v>
       </c>
       <c r="C107" s="8">
-        <v>459</v>
+        <v>479</v>
       </c>
     </row>
     <row r="108">
@@ -960,15 +960,15 @@
         <v>22</v>
       </c>
       <c r="C108" s="8">
-        <v>479</v>
+        <v>509</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="7">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="C109" s="8">
-        <v>479</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110">
@@ -976,23 +976,23 @@
         <v>22</v>
       </c>
       <c r="C110" s="8">
-        <v>509</v>
+        <v>575</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="7">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="C111" s="8">
-        <v>20</v>
+        <v>600</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C112" s="8">
-        <v>575</v>
+        <v>600</v>
       </c>
     </row>
     <row r="113">
@@ -1000,15 +1000,15 @@
         <v>22</v>
       </c>
       <c r="C113" s="8">
-        <v>600</v>
+        <v>642</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="7">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="C114" s="8">
-        <v>600</v>
+        <v>642</v>
       </c>
     </row>
     <row r="115">
@@ -1016,39 +1016,39 @@
         <v>22</v>
       </c>
       <c r="C115" s="8">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="7">
-        <v>264</v>
+        <v>24</v>
       </c>
       <c r="C116" s="8">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="7">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="C117" s="8">
-        <v>643</v>
+        <v>274</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="7">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="C118" s="8">
-        <v>643</v>
+        <v>276</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="7">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="C119" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120">
@@ -1056,124 +1056,124 @@
         <v>145</v>
       </c>
       <c r="C120" s="8">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="7">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="C121" s="8">
-        <v>279</v>
+        <v>603</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="7">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="C122" s="8">
-        <v>283</v>
+        <v>138</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="7">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="C123" s="8">
-        <v>603</v>
+        <v>241</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="7">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C124" s="8">
-        <v>138</v>
+        <v>461</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="7">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C125" s="8">
-        <v>241</v>
+        <v>462</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="7">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C126" s="8">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="7">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C127" s="8">
-        <v>462</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="7">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C128" s="8">
-        <v>462</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" s="7">
-        <v>56</v>
+        <v>248</v>
       </c>
       <c r="C129" s="8">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="7">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C130" s="8">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="7">
-        <v>248</v>
+        <v>71</v>
       </c>
       <c r="C131" s="8">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="7">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="C132" s="8">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" s="7">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C133" s="8">
-        <v>40</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="7">
-        <v>485</v>
+        <v>135</v>
       </c>
       <c r="C134" s="8">
-        <v>52</v>
+        <v>131</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="7">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C135" s="8">
         <v>131</v>
@@ -1181,98 +1181,98 @@
     </row>
     <row r="136">
       <c r="B136" s="7">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="C136" s="8">
-        <v>131</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="7">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C137" s="8">
-        <v>131</v>
+        <v>233</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="7">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="C138" s="8">
-        <v>233</v>
+        <v>417</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="7">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="C139" s="8">
-        <v>233</v>
+        <v>417</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="7">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C140" s="8">
-        <v>417</v>
+        <v>436</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="7">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="C141" s="8">
-        <v>417</v>
+        <v>436</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="7">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="C142" s="8">
-        <v>436</v>
+        <v>519</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="7">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C143" s="8">
-        <v>436</v>
+        <v>519</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" s="7">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="C144" s="8">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="7">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C145" s="8">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="7">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C146" s="8">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="7">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="C147" s="8">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="148">
@@ -1280,15 +1280,15 @@
         <v>43</v>
       </c>
       <c r="C148" s="8">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="7">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="C149" s="8">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="150">
@@ -1296,119 +1296,119 @@
         <v>43</v>
       </c>
       <c r="C150" s="8">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="7">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C151" s="8">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="7">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C152" s="8">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="7">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C153" s="8">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="7">
-        <v>32</v>
+        <v>313</v>
       </c>
       <c r="C154" s="8">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="7">
-        <v>56</v>
+        <v>311</v>
       </c>
       <c r="C155" s="8">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7">
-        <v>313</v>
+        <v>176</v>
       </c>
       <c r="C156" s="8">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="7">
-        <v>311</v>
+        <v>53</v>
       </c>
       <c r="C157" s="8">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="C158" s="8">
-        <v>533</v>
+        <v>554</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7">
-        <v>53</v>
+        <v>366</v>
       </c>
       <c r="C159" s="8">
-        <v>533</v>
+        <v>555</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C160" s="8">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7">
-        <v>366</v>
+        <v>313</v>
       </c>
       <c r="C161" s="8">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="C162" s="8">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C163" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="7">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="C164" s="8">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="165">
@@ -1416,223 +1416,223 @@
         <v>312</v>
       </c>
       <c r="C165" s="8">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7">
-        <v>312</v>
+        <v>88</v>
       </c>
       <c r="C166" s="8">
-        <v>558</v>
+        <v>569</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="7">
-        <v>312</v>
+        <v>111</v>
       </c>
       <c r="C167" s="8">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7">
-        <v>88</v>
+        <v>254</v>
       </c>
       <c r="C168" s="8">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="C169" s="8">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C170" s="8">
-        <v>570</v>
+        <v>713</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="7">
-        <v>252</v>
+        <v>469</v>
       </c>
       <c r="C171" s="8">
-        <v>571</v>
+        <v>712</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="7">
-        <v>296</v>
+        <v>117</v>
       </c>
       <c r="C172" s="8">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="7">
-        <v>469</v>
+        <v>117</v>
       </c>
       <c r="C173" s="8">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="7">
-        <v>117</v>
+        <v>468</v>
       </c>
       <c r="C174" s="8">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7">
-        <v>117</v>
+        <v>362</v>
       </c>
       <c r="C175" s="8">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="7">
-        <v>468</v>
+        <v>313</v>
       </c>
       <c r="C176" s="8">
-        <v>709</v>
+        <v>469</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="7">
-        <v>362</v>
+        <v>71</v>
       </c>
       <c r="C177" s="8">
-        <v>708</v>
+        <v>44</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="7">
-        <v>313</v>
+        <v>444</v>
       </c>
       <c r="C178" s="8">
-        <v>469</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="7">
-        <v>71</v>
+        <v>328</v>
       </c>
       <c r="C179" s="8">
-        <v>44</v>
+        <v>516</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="7">
-        <v>444</v>
+        <v>183</v>
       </c>
       <c r="C180" s="8">
-        <v>449</v>
+        <v>518</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" s="7">
-        <v>328</v>
+        <v>182</v>
       </c>
       <c r="C181" s="8">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="7">
-        <v>183</v>
+        <v>312</v>
       </c>
       <c r="C182" s="8">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" s="7">
-        <v>182</v>
+        <v>486</v>
       </c>
       <c r="C183" s="8">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="7">
-        <v>312</v>
+        <v>486</v>
       </c>
       <c r="C184" s="8">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" s="7">
-        <v>486</v>
+        <v>313</v>
       </c>
       <c r="C185" s="8">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" s="7">
-        <v>486</v>
+        <v>250</v>
       </c>
       <c r="C186" s="8">
-        <v>522</v>
+        <v>572</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" s="7">
-        <v>313</v>
+        <v>95</v>
       </c>
       <c r="C187" s="8">
-        <v>522</v>
+        <v>572</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="7">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="C188" s="8">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" s="7">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="C189" s="8">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" s="7">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="C190" s="8">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" s="7">
-        <v>328</v>
+        <v>95</v>
       </c>
       <c r="C191" s="8">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" s="7">
-        <v>461</v>
+        <v>19</v>
       </c>
       <c r="C192" s="8">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="193">
@@ -1640,20 +1640,20 @@
         <v>95</v>
       </c>
       <c r="C193" s="8">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" s="7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C194" s="8">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" s="7">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="C195" s="8">
         <v>578</v>
@@ -1661,114 +1661,114 @@
     </row>
     <row r="196">
       <c r="B196" s="7">
-        <v>33</v>
+        <v>218</v>
       </c>
       <c r="C196" s="8">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" s="7">
-        <v>59</v>
+        <v>417</v>
       </c>
       <c r="C197" s="8">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" s="7">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="C198" s="8">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" s="7">
-        <v>417</v>
+        <v>195</v>
       </c>
       <c r="C199" s="8">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="7">
-        <v>196</v>
+        <v>407</v>
       </c>
       <c r="C200" s="8">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" s="7">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="C201" s="8">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" s="7">
-        <v>407</v>
+        <v>127</v>
       </c>
       <c r="C202" s="8">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" s="7">
-        <v>126</v>
+        <v>429</v>
       </c>
       <c r="C203" s="8">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" s="7">
-        <v>127</v>
+        <v>429</v>
       </c>
       <c r="C204" s="8">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" s="7">
-        <v>429</v>
+        <v>120</v>
       </c>
       <c r="C205" s="8">
-        <v>584</v>
+        <v>593</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="7">
-        <v>429</v>
+        <v>120</v>
       </c>
       <c r="C206" s="8">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="7">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C207" s="8">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" s="7">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="C208" s="8">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="7">
-        <v>135</v>
+        <v>384</v>
       </c>
       <c r="C209" s="8">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="210">
@@ -1776,12 +1776,12 @@
         <v>49</v>
       </c>
       <c r="C210" s="8">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="7">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="C211" s="8">
         <v>596</v>
@@ -1789,26 +1789,26 @@
     </row>
     <row r="212">
       <c r="B212" s="7">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="C212" s="8">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" s="7">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C213" s="8">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="7">
-        <v>14</v>
+        <v>311</v>
       </c>
       <c r="C214" s="8">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="215">
@@ -1816,15 +1816,15 @@
         <v>10</v>
       </c>
       <c r="C215" s="8">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="7">
-        <v>311</v>
+        <v>209</v>
       </c>
       <c r="C216" s="8">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="217">
@@ -1832,23 +1832,23 @@
         <v>10</v>
       </c>
       <c r="C217" s="8">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="7">
-        <v>209</v>
+        <v>314</v>
       </c>
       <c r="C218" s="8">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" s="7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C219" s="8">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="220">
@@ -1856,239 +1856,239 @@
         <v>314</v>
       </c>
       <c r="C220" s="8">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" s="7">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C221" s="8">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C222" s="8">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="7">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="C223" s="8">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="7">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="C224" s="8">
-        <v>611</v>
+        <v>629</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" s="7">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C225" s="8">
-        <v>612</v>
+        <v>630</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="7">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C226" s="8">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="7">
-        <v>145</v>
+        <v>487</v>
       </c>
       <c r="C227" s="8">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="7">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="C228" s="8">
-        <v>631</v>
+        <v>260</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="7">
-        <v>487</v>
+        <v>195</v>
       </c>
       <c r="C229" s="8">
-        <v>633</v>
+        <v>260</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="7">
-        <v>196</v>
+        <v>16</v>
       </c>
       <c r="C230" s="8">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="7">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="C231" s="8">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="7">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="C232" s="8">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="7">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C233" s="8">
-        <v>264</v>
+        <v>294</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" s="7">
-        <v>104</v>
+        <v>328</v>
       </c>
       <c r="C234" s="8">
-        <v>272</v>
+        <v>296</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="7">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C235" s="8">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="7">
-        <v>328</v>
+        <v>439</v>
       </c>
       <c r="C236" s="8">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="7">
-        <v>328</v>
+        <v>33</v>
       </c>
       <c r="C237" s="8">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="7">
-        <v>439</v>
+        <v>34</v>
       </c>
       <c r="C238" s="8">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="7">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C239" s="8">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="7">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C240" s="8">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="7">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C241" s="8">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="7">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C242" s="8">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C243" s="8">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="7">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="C244" s="8">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C245" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="7">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="C246" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C247" s="8">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="7">
-        <v>238</v>
+        <v>38</v>
       </c>
       <c r="C248" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C249" s="8">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="250">
@@ -2096,39 +2096,39 @@
         <v>38</v>
       </c>
       <c r="C250" s="8">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="7">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="C251" s="8">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="7">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="C252" s="8">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" s="7">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="C253" s="8">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="7">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="C254" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="255">
@@ -2136,172 +2136,172 @@
         <v>312</v>
       </c>
       <c r="C255" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="7">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="C256" s="8">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="7">
-        <v>312</v>
+        <v>210</v>
       </c>
       <c r="C257" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="7">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="C258" s="8">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="7">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C259" s="8">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="7">
-        <v>196</v>
+        <v>417</v>
       </c>
       <c r="C260" s="8">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="7">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C261" s="8">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="7">
-        <v>417</v>
+        <v>125</v>
       </c>
       <c r="C262" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="7">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="C263" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="7">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C264" s="8">
-        <v>379</v>
+        <v>225</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="7">
-        <v>69</v>
+        <v>368</v>
       </c>
       <c r="C265" s="8">
-        <v>379</v>
+        <v>115</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="7">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C266" s="8">
-        <v>225</v>
+        <v>673</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="7">
-        <v>368</v>
+        <v>177</v>
       </c>
       <c r="C267" s="8">
-        <v>115</v>
+        <v>674</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="7">
-        <v>177</v>
+        <v>444</v>
       </c>
       <c r="C268" s="8">
-        <v>673</v>
+        <v>518</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="7">
-        <v>177</v>
+        <v>485</v>
       </c>
       <c r="C269" s="8">
-        <v>674</v>
+        <v>250</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="7">
-        <v>444</v>
+        <v>311</v>
       </c>
       <c r="C270" s="8">
-        <v>518</v>
+        <v>714</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="7">
-        <v>485</v>
+        <v>50</v>
       </c>
       <c r="C271" s="8">
-        <v>250</v>
+        <v>55</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="7">
-        <v>311</v>
+        <v>110</v>
       </c>
       <c r="C272" s="8">
-        <v>714</v>
+        <v>96</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" s="7">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="C273" s="8">
-        <v>55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C274" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" s="7">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C275" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" s="7">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="C276" s="8">
         <v>98</v>
@@ -2309,55 +2309,55 @@
     </row>
     <row r="277">
       <c r="B277" s="7">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C277" s="8">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="7">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C278" s="8">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" s="7">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C279" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" s="7">
-        <v>59</v>
+        <v>271</v>
       </c>
       <c r="C280" s="8">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" s="7">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="C281" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" s="7">
-        <v>271</v>
+        <v>127</v>
       </c>
       <c r="C282" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="7">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C283" s="8">
         <v>111</v>
@@ -2365,143 +2365,143 @@
     </row>
     <row r="284">
       <c r="B284" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C284" s="8">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" s="7">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C285" s="8">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" s="7">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C286" s="8">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" s="7">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C287" s="8">
-        <v>113</v>
+        <v>142</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" s="7">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C288" s="8">
-        <v>117</v>
+        <v>216</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" s="7">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C289" s="8">
-        <v>142</v>
+        <v>217</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" s="7">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="C290" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="7">
-        <v>166</v>
+        <v>445</v>
       </c>
       <c r="C291" s="8">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" s="7">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="C292" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" s="7">
-        <v>445</v>
+        <v>220</v>
       </c>
       <c r="C293" s="8">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="7">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="C294" s="8">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" s="7">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C295" s="8">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" s="7">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="C296" s="8">
-        <v>224</v>
+        <v>262</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" s="7">
-        <v>245</v>
+        <v>522</v>
       </c>
       <c r="C297" s="8">
-        <v>227</v>
+        <v>266</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" s="7">
-        <v>38</v>
+        <v>522</v>
       </c>
       <c r="C298" s="8">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="7">
-        <v>522</v>
+        <v>201</v>
       </c>
       <c r="C299" s="8">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" s="7">
-        <v>522</v>
+        <v>200</v>
       </c>
       <c r="C300" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="301">
       <c r="B301" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C301" s="8">
         <v>270</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="302">
       <c r="B302" s="7">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="C302" s="8">
         <v>270</v>
@@ -2517,18 +2517,18 @@
     </row>
     <row r="303">
       <c r="B303" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C303" s="8">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" s="7">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="C304" s="8">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="305">
@@ -2536,55 +2536,55 @@
         <v>209</v>
       </c>
       <c r="C305" s="8">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C306" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" s="7">
-        <v>209</v>
+        <v>313</v>
       </c>
       <c r="C307" s="8">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" s="7">
-        <v>209</v>
+        <v>36</v>
       </c>
       <c r="C308" s="8">
-        <v>289</v>
+        <v>318</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" s="7">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="C309" s="8">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" s="7">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C310" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" s="7">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C311" s="8">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="312">
@@ -2592,79 +2592,79 @@
         <v>53</v>
       </c>
       <c r="C312" s="8">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" s="7">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C313" s="8">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" s="7">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C314" s="8">
-        <v>324</v>
+        <v>342</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" s="7">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="C315" s="8">
-        <v>340</v>
+        <v>358</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" s="7">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="C316" s="8">
-        <v>342</v>
+        <v>361</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" s="7">
-        <v>123</v>
+        <v>384</v>
       </c>
       <c r="C317" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" s="7">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="C318" s="8">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" s="7">
-        <v>384</v>
+        <v>125</v>
       </c>
       <c r="C319" s="8">
-        <v>363</v>
+        <v>382</v>
       </c>
     </row>
     <row r="320">
       <c r="B320" s="7">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="C320" s="8">
-        <v>369</v>
+        <v>382</v>
       </c>
     </row>
     <row r="321">
       <c r="B321" s="7">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C321" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="322">
@@ -2672,7 +2672,7 @@
         <v>69</v>
       </c>
       <c r="C322" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="323">
@@ -2680,7 +2680,7 @@
         <v>106</v>
       </c>
       <c r="C323" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="324">
@@ -2688,15 +2688,15 @@
         <v>69</v>
       </c>
       <c r="C324" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="325">
       <c r="B325" s="7">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="C325" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="326">
@@ -2704,7 +2704,7 @@
         <v>69</v>
       </c>
       <c r="C326" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="327">
@@ -2712,7 +2712,7 @@
         <v>49</v>
       </c>
       <c r="C327" s="8">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="328">
@@ -2720,28 +2720,28 @@
         <v>69</v>
       </c>
       <c r="C328" s="8">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="329">
       <c r="B329" s="7">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C329" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="330">
       <c r="B330" s="7">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C330" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="331">
       <c r="B331" s="7">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C331" s="8">
         <v>392</v>
@@ -2749,39 +2749,39 @@
     </row>
     <row r="332">
       <c r="B332" s="7">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C332" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="333">
       <c r="B333" s="7">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C333" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="334">
       <c r="B334" s="7">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C334" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="335">
       <c r="B335" s="7">
-        <v>123</v>
+        <v>429</v>
       </c>
       <c r="C335" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="336">
       <c r="B336" s="7">
-        <v>119</v>
+        <v>489</v>
       </c>
       <c r="C336" s="8">
         <v>395</v>
@@ -2789,23 +2789,23 @@
     </row>
     <row r="337">
       <c r="B337" s="7">
-        <v>429</v>
+        <v>27</v>
       </c>
       <c r="C337" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="338">
       <c r="B338" s="7">
-        <v>489</v>
+        <v>323</v>
       </c>
       <c r="C338" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="339">
       <c r="B339" s="7">
-        <v>27</v>
+        <v>324</v>
       </c>
       <c r="C339" s="8">
         <v>397</v>
@@ -2813,7 +2813,7 @@
     </row>
     <row r="340">
       <c r="B340" s="7">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="C340" s="8">
         <v>397</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="341">
       <c r="B341" s="7">
-        <v>324</v>
+        <v>59</v>
       </c>
       <c r="C341" s="8">
         <v>397</v>
@@ -2829,42 +2829,42 @@
     </row>
     <row r="342">
       <c r="B342" s="7">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="C342" s="8">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="343">
       <c r="B343" s="7">
-        <v>59</v>
+        <v>221</v>
       </c>
       <c r="C343" s="8">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="344">
       <c r="B344" s="7">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="C344" s="8">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="345">
       <c r="B345" s="7">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C345" s="8">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="346">
       <c r="B346" s="7">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C346" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="347">
@@ -2872,36 +2872,36 @@
         <v>163</v>
       </c>
       <c r="C347" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="348">
       <c r="B348" s="7">
-        <v>89</v>
+        <v>328</v>
       </c>
       <c r="C348" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="349">
       <c r="B349" s="7">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C349" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="350">
       <c r="B350" s="7">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C350" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="351">
       <c r="B351" s="7">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="C351" s="8">
         <v>413</v>
@@ -2909,34 +2909,34 @@
     </row>
     <row r="352">
       <c r="B352" s="7">
-        <v>338</v>
+        <v>248</v>
       </c>
       <c r="C352" s="8">
-        <v>413</v>
+        <v>442</v>
       </c>
     </row>
     <row r="353">
       <c r="B353" s="7">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C353" s="8">
-        <v>413</v>
+        <v>639</v>
       </c>
     </row>
     <row r="354">
       <c r="B354" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C354" s="8">
-        <v>442</v>
+        <v>639</v>
       </c>
     </row>
     <row r="355">
       <c r="B355" s="7">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C355" s="8">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="356">
@@ -2944,36 +2944,36 @@
         <v>247</v>
       </c>
       <c r="C356" s="8">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="357">
       <c r="B357" s="7">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="C357" s="8">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="358">
       <c r="B358" s="7">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="C358" s="8">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="359">
       <c r="B359" s="7">
-        <v>328</v>
+        <v>384</v>
       </c>
       <c r="C359" s="8">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="360">
       <c r="B360" s="7">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="C360" s="8">
         <v>644</v>
@@ -2981,23 +2981,23 @@
     </row>
     <row r="361">
       <c r="B361" s="7">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="C361" s="8">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="362">
       <c r="B362" s="7">
-        <v>312</v>
+        <v>183</v>
       </c>
       <c r="C362" s="8">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="363">
       <c r="B363" s="7">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="C363" s="8">
         <v>645</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="364">
       <c r="B364" s="7">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C364" s="8">
         <v>645</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="365">
       <c r="B365" s="7">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="C365" s="8">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="366">
@@ -3024,23 +3024,23 @@
         <v>123</v>
       </c>
       <c r="C366" s="8">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="367">
       <c r="B367" s="7">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="C367" s="8">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="368">
       <c r="B368" s="7">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="C368" s="8">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="369">
@@ -3048,36 +3048,36 @@
         <v>123</v>
       </c>
       <c r="C369" s="8">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="370">
       <c r="B370" s="7">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="C370" s="8">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="371">
       <c r="B371" s="7">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C371" s="8">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="372">
       <c r="B372" s="7">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C372" s="8">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="373">
       <c r="B373" s="7">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C373" s="8">
         <v>649</v>
@@ -3088,7 +3088,7 @@
         <v>123</v>
       </c>
       <c r="C374" s="8">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="375">
@@ -3096,12 +3096,12 @@
         <v>105</v>
       </c>
       <c r="C375" s="8">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="376">
       <c r="B376" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C376" s="8">
         <v>650</v>
@@ -3109,55 +3109,55 @@
     </row>
     <row r="377">
       <c r="B377" s="7">
-        <v>105</v>
+        <v>339</v>
       </c>
       <c r="C377" s="8">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="378">
       <c r="B378" s="7">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C378" s="8">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="379">
       <c r="B379" s="7">
-        <v>339</v>
+        <v>64</v>
       </c>
       <c r="C379" s="8">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="380">
       <c r="B380" s="7">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C380" s="8">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="381">
       <c r="B381" s="7">
-        <v>64</v>
+        <v>274</v>
       </c>
       <c r="C381" s="8">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="382">
       <c r="B382" s="7">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="C382" s="8">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="383">
       <c r="B383" s="7">
-        <v>274</v>
+        <v>120</v>
       </c>
       <c r="C383" s="8">
         <v>654</v>
@@ -3165,26 +3165,26 @@
     </row>
     <row r="384">
       <c r="B384" s="7">
-        <v>64</v>
+        <v>459</v>
       </c>
       <c r="C384" s="8">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="385">
       <c r="B385" s="7">
-        <v>120</v>
+        <v>231</v>
       </c>
       <c r="C385" s="8">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="386">
       <c r="B386" s="7">
-        <v>459</v>
+        <v>127</v>
       </c>
       <c r="C386" s="8">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="387">
@@ -3192,15 +3192,15 @@
         <v>231</v>
       </c>
       <c r="C387" s="8">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="388">
       <c r="B388" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C388" s="8">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="389">
@@ -3208,188 +3208,188 @@
         <v>231</v>
       </c>
       <c r="C389" s="8">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="390">
       <c r="B390" s="7">
-        <v>126</v>
+        <v>286</v>
       </c>
       <c r="C390" s="8">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="391">
       <c r="B391" s="7">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="C391" s="8">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="392">
       <c r="B392" s="7">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C392" s="8">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="393">
       <c r="B393" s="7">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="C393" s="8">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="394">
       <c r="B394" s="7">
-        <v>274</v>
+        <v>59</v>
       </c>
       <c r="C394" s="8">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="395">
       <c r="B395" s="7">
-        <v>229</v>
+        <v>65</v>
       </c>
       <c r="C395" s="8">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="396">
       <c r="B396" s="7">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C396" s="8">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="397">
       <c r="B397" s="7">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C397" s="8">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="398">
       <c r="B398" s="7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C398" s="8">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="399">
       <c r="B399" s="7">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="C399" s="8">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="400">
       <c r="B400" s="7">
-        <v>60</v>
+        <v>523</v>
       </c>
       <c r="C400" s="8">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="401">
       <c r="B401" s="7">
-        <v>60</v>
+        <v>501</v>
       </c>
       <c r="C401" s="8">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="402">
       <c r="B402" s="7">
-        <v>523</v>
+        <v>169</v>
       </c>
       <c r="C402" s="8">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="403">
       <c r="B403" s="7">
-        <v>501</v>
+        <v>59</v>
       </c>
       <c r="C403" s="8">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="404">
       <c r="B404" s="7">
-        <v>169</v>
+        <v>10</v>
       </c>
       <c r="C404" s="8">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="405">
       <c r="B405" s="7">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="C405" s="8">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="406">
       <c r="B406" s="7">
-        <v>10</v>
+        <v>524</v>
       </c>
       <c r="C406" s="8">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="407">
       <c r="B407" s="7">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="C407" s="8">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="408">
       <c r="B408" s="7">
-        <v>524</v>
+        <v>23</v>
       </c>
       <c r="C408" s="8">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="409">
       <c r="B409" s="7">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C409" s="8">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="410">
       <c r="B410" s="7">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="C410" s="8">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="411">
       <c r="B411" s="7">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C411" s="8">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="412">
       <c r="B412" s="7">
-        <v>209</v>
+        <v>16</v>
       </c>
       <c r="C412" s="8">
         <v>679</v>
@@ -3397,42 +3397,42 @@
     </row>
     <row r="413">
       <c r="B413" s="7">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="C413" s="8">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="414">
       <c r="B414" s="7">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C414" s="8">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="415">
       <c r="B415" s="7">
-        <v>164</v>
+        <v>445</v>
       </c>
       <c r="C415" s="8">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="416">
       <c r="B416" s="7">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="C416" s="8">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="417">
       <c r="B417" s="7">
-        <v>445</v>
+        <v>525</v>
       </c>
       <c r="C417" s="8">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="418">
@@ -3440,84 +3440,84 @@
         <v>55</v>
       </c>
       <c r="C418" s="8">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="419">
       <c r="B419" s="7">
-        <v>525</v>
+        <v>60</v>
       </c>
       <c r="C419" s="8">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="420">
       <c r="B420" s="7">
-        <v>55</v>
+        <v>231</v>
       </c>
       <c r="C420" s="8">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="421">
       <c r="B421" s="7">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C421" s="8">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="422">
       <c r="B422" s="7">
-        <v>231</v>
+        <v>60</v>
       </c>
       <c r="C422" s="8">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="423">
       <c r="B423" s="7">
-        <v>97</v>
+        <v>459</v>
       </c>
       <c r="C423" s="8">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="424">
       <c r="B424" s="7">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c r="C424" s="8">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="425">
       <c r="B425" s="7">
-        <v>459</v>
+        <v>16</v>
       </c>
       <c r="C425" s="8">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="426">
       <c r="B426" s="7">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C426" s="8">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="427">
       <c r="B427" s="7">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="C427" s="8">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="428">
       <c r="B428" s="7">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="C428" s="8">
         <v>698</v>
@@ -3525,18 +3525,18 @@
     </row>
     <row r="429">
       <c r="B429" s="7">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="C429" s="8">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="430">
       <c r="B430" s="7">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="C430" s="8">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="431">
@@ -3544,31 +3544,31 @@
         <v>328</v>
       </c>
       <c r="C431" s="8">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="432">
       <c r="B432" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C432" s="8">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="433">
       <c r="B433" s="7">
-        <v>328</v>
+        <v>152</v>
       </c>
       <c r="C433" s="8">
-        <v>700</v>
+        <v>157</v>
       </c>
     </row>
     <row r="434">
       <c r="B434" s="7">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="C434" s="8">
-        <v>700</v>
+        <v>157</v>
       </c>
     </row>
     <row r="435">
@@ -3576,39 +3576,39 @@
         <v>152</v>
       </c>
       <c r="C435" s="8">
-        <v>157</v>
+        <v>294</v>
       </c>
     </row>
     <row r="436">
       <c r="B436" s="7">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="C436" s="8">
-        <v>157</v>
+        <v>552</v>
       </c>
     </row>
     <row r="437">
       <c r="B437" s="7">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="C437" s="8">
-        <v>294</v>
+        <v>552</v>
       </c>
     </row>
     <row r="438">
       <c r="B438" s="7">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C438" s="8">
-        <v>552</v>
+        <v>726</v>
       </c>
     </row>
     <row r="439">
       <c r="B439" s="7">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C439" s="8">
-        <v>552</v>
+        <v>727</v>
       </c>
     </row>
     <row r="440">
@@ -3616,7 +3616,7 @@
         <v>22</v>
       </c>
       <c r="C440" s="8">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="441">
@@ -3624,28 +3624,28 @@
         <v>22</v>
       </c>
       <c r="C441" s="8">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="442">
       <c r="B442" s="7">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="C442" s="8">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="443">
       <c r="B443" s="7">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="C443" s="8">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="444">
       <c r="B444" s="7">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C444" s="8">
         <v>730</v>
@@ -3653,18 +3653,18 @@
     </row>
     <row r="445">
       <c r="B445" s="7">
-        <v>226</v>
+        <v>23</v>
       </c>
       <c r="C445" s="8">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="446">
       <c r="B446" s="7">
-        <v>234</v>
+        <v>22</v>
       </c>
       <c r="C446" s="8">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="447">
@@ -3672,7 +3672,7 @@
         <v>23</v>
       </c>
       <c r="C447" s="8">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="448">
@@ -3680,23 +3680,23 @@
         <v>22</v>
       </c>
       <c r="C448" s="8">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="449">
       <c r="B449" s="7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C449" s="8">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="450">
       <c r="B450" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C450" s="8">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="451">
@@ -3704,7 +3704,7 @@
         <v>22</v>
       </c>
       <c r="C451" s="8">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="452">
@@ -3712,15 +3712,15 @@
         <v>23</v>
       </c>
       <c r="C452" s="8">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="453">
       <c r="B453" s="7">
-        <v>22</v>
+        <v>209</v>
       </c>
       <c r="C453" s="8">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="454">
@@ -3728,7 +3728,7 @@
         <v>23</v>
       </c>
       <c r="C454" s="8">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="455">
@@ -3736,7 +3736,7 @@
         <v>209</v>
       </c>
       <c r="C455" s="8">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="456">
@@ -3744,28 +3744,28 @@
         <v>23</v>
       </c>
       <c r="C456" s="8">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="457">
       <c r="B457" s="7">
-        <v>209</v>
+        <v>16</v>
       </c>
       <c r="C457" s="8">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="458">
       <c r="B458" s="7">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="C458" s="8">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="459">
       <c r="B459" s="7">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C459" s="8">
         <v>737</v>
@@ -3773,34 +3773,34 @@
     </row>
     <row r="460">
       <c r="B460" s="7">
-        <v>209</v>
+        <v>359</v>
       </c>
       <c r="C460" s="8">
-        <v>737</v>
+        <v>445</v>
       </c>
     </row>
     <row r="461">
       <c r="B461" s="7">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="C461" s="8">
-        <v>737</v>
+        <v>445</v>
       </c>
     </row>
     <row r="462">
       <c r="B462" s="7">
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="C462" s="8">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="463">
       <c r="B463" s="7">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="C463" s="8">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="464">
@@ -3808,39 +3808,39 @@
         <v>313</v>
       </c>
       <c r="C464" s="8">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="465">
       <c r="B465" s="7">
-        <v>359</v>
+        <v>214</v>
       </c>
       <c r="C465" s="8">
-        <v>447</v>
+        <v>714</v>
       </c>
     </row>
     <row r="466">
       <c r="B466" s="7">
-        <v>313</v>
+        <v>216</v>
       </c>
       <c r="C466" s="8">
-        <v>447</v>
+        <v>715</v>
       </c>
     </row>
     <row r="467">
       <c r="B467" s="7">
-        <v>214</v>
+        <v>311</v>
       </c>
       <c r="C467" s="8">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="468">
       <c r="B468" s="7">
-        <v>216</v>
+        <v>311</v>
       </c>
       <c r="C468" s="8">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="469">
@@ -3848,7 +3848,7 @@
         <v>311</v>
       </c>
       <c r="C469" s="8">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="470">
@@ -3856,23 +3856,23 @@
         <v>311</v>
       </c>
       <c r="C470" s="8">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="471">
       <c r="B471" s="7">
-        <v>311</v>
+        <v>22</v>
       </c>
       <c r="C471" s="8">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="472">
       <c r="B472" s="7">
-        <v>311</v>
+        <v>22</v>
       </c>
       <c r="C472" s="8">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="473">
@@ -3880,15 +3880,15 @@
         <v>22</v>
       </c>
       <c r="C473" s="8">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="474">
       <c r="B474" s="7">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C474" s="8">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="475">
@@ -3896,31 +3896,343 @@
         <v>22</v>
       </c>
       <c r="C475" s="8">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="476">
       <c r="B476" s="7">
-        <v>48</v>
+        <v>328</v>
       </c>
       <c r="C476" s="8">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="477">
       <c r="B477" s="7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C477" s="8">
-        <v>724</v>
+        <v>25</v>
       </c>
     </row>
     <row r="478">
       <c r="B478" s="7">
-        <v>328</v>
+        <v>14</v>
       </c>
       <c r="C478" s="8">
-        <v>725</v>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" s="7">
+        <v>177</v>
+      </c>
+      <c r="C479" s="8">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" s="7">
+        <v>17</v>
+      </c>
+      <c r="C480" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" s="7">
+        <v>118</v>
+      </c>
+      <c r="C481" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" s="7">
+        <v>16</v>
+      </c>
+      <c r="C482" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" s="7">
+        <v>23</v>
+      </c>
+      <c r="C483" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" s="7">
+        <v>62</v>
+      </c>
+      <c r="C484" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" s="7">
+        <v>26</v>
+      </c>
+      <c r="C485" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" s="7">
+        <v>56</v>
+      </c>
+      <c r="C486" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" s="7">
+        <v>35</v>
+      </c>
+      <c r="C487" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" s="7">
+        <v>527</v>
+      </c>
+      <c r="C488" s="8">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" s="7">
+        <v>509</v>
+      </c>
+      <c r="C489" s="8">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" s="7">
+        <v>458</v>
+      </c>
+      <c r="C490" s="8">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" s="7">
+        <v>137</v>
+      </c>
+      <c r="C491" s="8">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" s="7">
+        <v>62</v>
+      </c>
+      <c r="C492" s="8">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" s="7">
+        <v>164</v>
+      </c>
+      <c r="C493" s="8">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" s="7">
+        <v>164</v>
+      </c>
+      <c r="C494" s="8">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" s="7">
+        <v>56</v>
+      </c>
+      <c r="C495" s="8">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" s="7">
+        <v>35</v>
+      </c>
+      <c r="C496" s="8">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" s="7">
+        <v>324</v>
+      </c>
+      <c r="C497" s="8">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" s="7">
+        <v>118</v>
+      </c>
+      <c r="C498" s="8">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" s="7">
+        <v>117</v>
+      </c>
+      <c r="C499" s="8">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" s="7">
+        <v>312</v>
+      </c>
+      <c r="C500" s="8">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" s="7">
+        <v>36</v>
+      </c>
+      <c r="C501" s="8">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" s="7">
+        <v>314</v>
+      </c>
+      <c r="C502" s="8">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" s="7">
+        <v>123</v>
+      </c>
+      <c r="C503" s="8">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" s="7">
+        <v>227</v>
+      </c>
+      <c r="C504" s="8">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" s="7">
+        <v>227</v>
+      </c>
+      <c r="C505" s="8">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" s="7">
+        <v>123</v>
+      </c>
+      <c r="C506" s="8">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" s="7">
+        <v>24</v>
+      </c>
+      <c r="C507" s="8">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" s="7">
+        <v>22</v>
+      </c>
+      <c r="C508" s="8">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" s="7">
+        <v>23</v>
+      </c>
+      <c r="C509" s="8">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" s="7">
+        <v>312</v>
+      </c>
+      <c r="C510" s="8">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" s="7">
+        <v>49</v>
+      </c>
+      <c r="C511" s="8">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" s="7">
+        <v>312</v>
+      </c>
+      <c r="C512" s="8">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" s="7">
+        <v>23</v>
+      </c>
+      <c r="C513" s="8">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" s="7">
+        <v>49</v>
+      </c>
+      <c r="C514" s="8">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" s="7">
+        <v>428</v>
+      </c>
+      <c r="C515" s="8">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" s="7">
+        <v>415</v>
+      </c>
+      <c r="C516" s="8">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" s="7">
+        <v>49</v>
+      </c>
+      <c r="C517" s="8">
+        <v>749</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -4235,6 +4235,318 @@
         <v>749</v>
       </c>
     </row>
+    <row r="518">
+      <c r="B518" s="7">
+        <v>140</v>
+      </c>
+      <c r="C518" s="8">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" s="7">
+        <v>444</v>
+      </c>
+      <c r="C519" s="8">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" s="7">
+        <v>132</v>
+      </c>
+      <c r="C520" s="8">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" s="7">
+        <v>365</v>
+      </c>
+      <c r="C521" s="8">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" s="7">
+        <v>266</v>
+      </c>
+      <c r="C522" s="8">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" s="7">
+        <v>262</v>
+      </c>
+      <c r="C523" s="8">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" s="7">
+        <v>540</v>
+      </c>
+      <c r="C524" s="8">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" s="7">
+        <v>324</v>
+      </c>
+      <c r="C525" s="8">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" s="7">
+        <v>287</v>
+      </c>
+      <c r="C526" s="8">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" s="7">
+        <v>552</v>
+      </c>
+      <c r="C527" s="8">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" s="7">
+        <v>561</v>
+      </c>
+      <c r="C528" s="8">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" s="7">
+        <v>27</v>
+      </c>
+      <c r="C529" s="8">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" s="7">
+        <v>27</v>
+      </c>
+      <c r="C530" s="8">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" s="7">
+        <v>141</v>
+      </c>
+      <c r="C531" s="8">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" s="7">
+        <v>141</v>
+      </c>
+      <c r="C532" s="8">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" s="7">
+        <v>141</v>
+      </c>
+      <c r="C533" s="8">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" s="7">
+        <v>141</v>
+      </c>
+      <c r="C534" s="8">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" s="7">
+        <v>365</v>
+      </c>
+      <c r="C535" s="8">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" s="7">
+        <v>365</v>
+      </c>
+      <c r="C536" s="8">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" s="7">
+        <v>365</v>
+      </c>
+      <c r="C537" s="8">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" s="7">
+        <v>64</v>
+      </c>
+      <c r="C538" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" s="7">
+        <v>541</v>
+      </c>
+      <c r="C539" s="8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" s="7">
+        <v>287</v>
+      </c>
+      <c r="C540" s="8">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" s="7">
+        <v>141</v>
+      </c>
+      <c r="C541" s="8">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" s="7">
+        <v>35</v>
+      </c>
+      <c r="C542" s="8">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" s="7">
+        <v>390</v>
+      </c>
+      <c r="C543" s="8">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" s="7">
+        <v>135</v>
+      </c>
+      <c r="C544" s="8">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" s="7">
+        <v>311</v>
+      </c>
+      <c r="C545" s="8">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" s="7">
+        <v>485</v>
+      </c>
+      <c r="C546" s="8">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" s="7">
+        <v>311</v>
+      </c>
+      <c r="C547" s="8">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" s="7">
+        <v>310</v>
+      </c>
+      <c r="C548" s="8">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" s="7">
+        <v>214</v>
+      </c>
+      <c r="C549" s="8">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" s="7">
+        <v>53</v>
+      </c>
+      <c r="C550" s="8">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" s="7">
+        <v>252</v>
+      </c>
+      <c r="C551" s="8">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" s="7">
+        <v>62</v>
+      </c>
+      <c r="C552" s="8">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" s="7">
+        <v>254</v>
+      </c>
+      <c r="C553" s="8">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" s="7">
+        <v>17</v>
+      </c>
+      <c r="C554" s="8">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" s="7">
+        <v>196</v>
+      </c>
+      <c r="C555" s="8">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" s="7">
+        <v>59</v>
+      </c>
+      <c r="C556" s="8">
+        <v>483</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -309,7 +309,7 @@
     </row>
     <row r="27">
       <c r="B27" s="7">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="C27" s="8">
         <v>454</v>
@@ -317,31 +317,31 @@
     </row>
     <row r="28">
       <c r="B28" s="7">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="C28" s="8">
-        <v>454</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="7">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C29" s="8">
-        <v>245</v>
+        <v>468</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="C30" s="8">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C31" s="8">
         <v>480</v>
@@ -349,63 +349,63 @@
     </row>
     <row r="32">
       <c r="B32" s="7">
-        <v>165</v>
+        <v>263</v>
       </c>
       <c r="C32" s="8">
-        <v>480</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C33" s="8">
-        <v>22</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="C34" s="8">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7">
-        <v>323</v>
+        <v>163</v>
       </c>
       <c r="C35" s="8">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="7">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C36" s="8">
-        <v>515</v>
+        <v>531</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="C37" s="8">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="7">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C38" s="8">
-        <v>534</v>
+        <v>451</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C39" s="8">
         <v>451</v>
@@ -413,7 +413,7 @@
     </row>
     <row r="40">
       <c r="B40" s="7">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="C40" s="8">
         <v>451</v>
@@ -421,15 +421,15 @@
     </row>
     <row r="41">
       <c r="B41" s="7">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="C41" s="8">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="7">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="C42" s="8">
         <v>455</v>
@@ -437,15 +437,15 @@
     </row>
     <row r="43">
       <c r="B43" s="7">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="C43" s="8">
-        <v>455</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="7">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="C44" s="8">
         <v>310</v>
@@ -453,15 +453,15 @@
     </row>
     <row r="45">
       <c r="B45" s="7">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="C45" s="8">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="7">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="C46" s="8">
         <v>313</v>
@@ -469,23 +469,23 @@
     </row>
     <row r="47">
       <c r="B47" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C47" s="8">
-        <v>313</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="7">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="C48" s="8">
-        <v>56</v>
+        <v>574</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="7">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="C49" s="8">
         <v>574</v>
@@ -493,15 +493,15 @@
     </row>
     <row r="50">
       <c r="B50" s="7">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="C50" s="8">
-        <v>574</v>
+        <v>597</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="7">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="C51" s="8">
         <v>597</v>
@@ -509,34 +509,34 @@
     </row>
     <row r="52">
       <c r="B52" s="7">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="C52" s="8">
-        <v>597</v>
+        <v>463</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C53" s="8">
-        <v>463</v>
+        <v>618</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C54" s="8">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="C55" s="8">
-        <v>617</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
@@ -544,12 +544,12 @@
         <v>271</v>
       </c>
       <c r="C56" s="8">
-        <v>25</v>
+        <v>628</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="C57" s="8">
         <v>628</v>
@@ -557,31 +557,31 @@
     </row>
     <row r="58">
       <c r="B58" s="7">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="C58" s="8">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="C59" s="8">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="7">
-        <v>55</v>
+        <v>277</v>
       </c>
       <c r="C60" s="8">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="7">
-        <v>277</v>
+        <v>117</v>
       </c>
       <c r="C61" s="8">
         <v>625</v>
@@ -589,10 +589,10 @@
     </row>
     <row r="62">
       <c r="B62" s="7">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="C62" s="8">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="63">
@@ -600,63 +600,63 @@
         <v>60</v>
       </c>
       <c r="C63" s="8">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="7">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C64" s="8">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="7">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="C65" s="8">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="7">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C66" s="8">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="7">
-        <v>158</v>
+        <v>361</v>
       </c>
       <c r="C67" s="8">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="7">
-        <v>361</v>
+        <v>137</v>
       </c>
       <c r="C68" s="8">
-        <v>616</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="7">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="C69" s="8">
-        <v>100</v>
+        <v>615</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="7">
-        <v>69</v>
+        <v>313</v>
       </c>
       <c r="C70" s="8">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="71">
@@ -664,12 +664,12 @@
         <v>313</v>
       </c>
       <c r="C71" s="8">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="7">
-        <v>313</v>
+        <v>59</v>
       </c>
       <c r="C72" s="8">
         <v>613</v>
@@ -677,15 +677,15 @@
     </row>
     <row r="73">
       <c r="B73" s="7">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="C73" s="8">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="7">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="C74" s="8">
         <v>607</v>
@@ -693,15 +693,15 @@
     </row>
     <row r="75">
       <c r="B75" s="7">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="C75" s="8">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="7">
-        <v>363</v>
+        <v>204</v>
       </c>
       <c r="C76" s="8">
         <v>606</v>
@@ -709,15 +709,15 @@
     </row>
     <row r="77">
       <c r="B77" s="7">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="C77" s="8">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="7">
-        <v>55</v>
+        <v>255</v>
       </c>
       <c r="C78" s="8">
         <v>605</v>
@@ -725,15 +725,15 @@
     </row>
     <row r="79">
       <c r="B79" s="7">
-        <v>255</v>
+        <v>458</v>
       </c>
       <c r="C79" s="8">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="7">
-        <v>458</v>
+        <v>22</v>
       </c>
       <c r="C80" s="8">
         <v>604</v>
@@ -741,47 +741,47 @@
     </row>
     <row r="81">
       <c r="B81" s="7">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="C81" s="8">
-        <v>604</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="7">
-        <v>104</v>
+        <v>248</v>
       </c>
       <c r="C82" s="8">
-        <v>85</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="7">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C83" s="8">
-        <v>37</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="7">
-        <v>226</v>
+        <v>60</v>
       </c>
       <c r="C84" s="8">
-        <v>366</v>
+        <v>652</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="7">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C85" s="8">
-        <v>652</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="7">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c r="C86" s="8">
         <v>149</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="87">
       <c r="B87" s="7">
-        <v>309</v>
+        <v>47</v>
       </c>
       <c r="C87" s="8">
         <v>149</v>
@@ -797,39 +797,39 @@
     </row>
     <row r="88">
       <c r="B88" s="7">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="C88" s="8">
-        <v>149</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="7">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="C89" s="8">
-        <v>107</v>
+        <v>462</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="7">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="C90" s="8">
-        <v>462</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="7">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="C91" s="8">
-        <v>14</v>
+        <v>646</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="7">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C92" s="8">
         <v>646</v>
@@ -837,18 +837,18 @@
     </row>
     <row r="93">
       <c r="B93" s="7">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="C93" s="8">
-        <v>646</v>
+        <v>587</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="7">
-        <v>480</v>
+        <v>140</v>
       </c>
       <c r="C94" s="8">
-        <v>587</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95">
@@ -856,7 +856,7 @@
         <v>140</v>
       </c>
       <c r="C95" s="8">
-        <v>119</v>
+        <v>538</v>
       </c>
     </row>
     <row r="96">
@@ -864,23 +864,23 @@
         <v>140</v>
       </c>
       <c r="C96" s="8">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="7">
-        <v>140</v>
+        <v>363</v>
       </c>
       <c r="C97" s="8">
-        <v>539</v>
+        <v>463</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="7">
-        <v>363</v>
+        <v>55</v>
       </c>
       <c r="C98" s="8">
-        <v>463</v>
+        <v>561</v>
       </c>
     </row>
     <row r="99">
@@ -888,12 +888,12 @@
         <v>55</v>
       </c>
       <c r="C99" s="8">
-        <v>561</v>
+        <v>682</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="7">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C100" s="8">
         <v>682</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="101">
       <c r="B101" s="7">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="C101" s="8">
-        <v>682</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102">
@@ -912,7 +912,7 @@
         <v>22</v>
       </c>
       <c r="C102" s="8">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103">
@@ -920,12 +920,12 @@
         <v>22</v>
       </c>
       <c r="C103" s="8">
-        <v>20</v>
+        <v>459</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="7">
-        <v>22</v>
+        <v>458</v>
       </c>
       <c r="C104" s="8">
         <v>459</v>
@@ -933,15 +933,15 @@
     </row>
     <row r="105">
       <c r="B105" s="7">
-        <v>458</v>
+        <v>22</v>
       </c>
       <c r="C105" s="8">
-        <v>459</v>
+        <v>479</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="7">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="C106" s="8">
         <v>479</v>
@@ -949,26 +949,26 @@
     </row>
     <row r="107">
       <c r="B107" s="7">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="C107" s="8">
-        <v>479</v>
+        <v>509</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="7">
-        <v>22</v>
+        <v>264</v>
       </c>
       <c r="C108" s="8">
-        <v>509</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="7">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="C109" s="8">
-        <v>20</v>
+        <v>575</v>
       </c>
     </row>
     <row r="110">
@@ -976,12 +976,12 @@
         <v>22</v>
       </c>
       <c r="C110" s="8">
-        <v>575</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C111" s="8">
         <v>600</v>
@@ -989,15 +989,15 @@
     </row>
     <row r="112">
       <c r="B112" s="7">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C112" s="8">
-        <v>600</v>
+        <v>642</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="7">
-        <v>22</v>
+        <v>264</v>
       </c>
       <c r="C113" s="8">
         <v>642</v>
@@ -1005,15 +1005,15 @@
     </row>
     <row r="114">
       <c r="B114" s="7">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="C114" s="8">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C115" s="8">
         <v>643</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="116">
       <c r="B116" s="7">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="C116" s="8">
-        <v>643</v>
+        <v>274</v>
       </c>
     </row>
     <row r="117">
@@ -1032,23 +1032,23 @@
         <v>145</v>
       </c>
       <c r="C117" s="8">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="7">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="C118" s="8">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="7">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="C119" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="120">
@@ -1056,15 +1056,15 @@
         <v>145</v>
       </c>
       <c r="C120" s="8">
-        <v>283</v>
+        <v>603</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="7">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="C121" s="8">
-        <v>603</v>
+        <v>138</v>
       </c>
     </row>
     <row r="122">
@@ -1072,28 +1072,28 @@
         <v>43</v>
       </c>
       <c r="C122" s="8">
-        <v>138</v>
+        <v>241</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="7">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C123" s="8">
-        <v>241</v>
+        <v>461</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="7">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C124" s="8">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="7">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C125" s="8">
         <v>462</v>
@@ -1101,15 +1101,15 @@
     </row>
     <row r="126">
       <c r="B126" s="7">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C126" s="8">
-        <v>462</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="7">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C127" s="8">
         <v>28</v>
@@ -1117,47 +1117,47 @@
     </row>
     <row r="128">
       <c r="B128" s="7">
+        <v>248</v>
+      </c>
+      <c r="C128" s="8">
         <v>35</v>
-      </c>
-      <c r="C128" s="8">
-        <v>28</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" s="7">
-        <v>248</v>
+        <v>16</v>
       </c>
       <c r="C129" s="8">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="7">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C130" s="8">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="7">
-        <v>71</v>
+        <v>485</v>
       </c>
       <c r="C131" s="8">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="7">
-        <v>485</v>
+        <v>59</v>
       </c>
       <c r="C132" s="8">
-        <v>52</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" s="7">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="C133" s="8">
         <v>131</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="134">
       <c r="B134" s="7">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="C134" s="8">
         <v>131</v>
@@ -1173,15 +1173,15 @@
     </row>
     <row r="135">
       <c r="B135" s="7">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C135" s="8">
-        <v>131</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="7">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C136" s="8">
         <v>233</v>
@@ -1189,15 +1189,15 @@
     </row>
     <row r="137">
       <c r="B137" s="7">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="C137" s="8">
-        <v>233</v>
+        <v>417</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C138" s="8">
         <v>417</v>
@@ -1205,15 +1205,15 @@
     </row>
     <row r="139">
       <c r="B139" s="7">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C139" s="8">
-        <v>417</v>
+        <v>436</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="7">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="C140" s="8">
         <v>436</v>
@@ -1221,15 +1221,15 @@
     </row>
     <row r="141">
       <c r="B141" s="7">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="C141" s="8">
-        <v>436</v>
+        <v>519</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="7">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="C142" s="8">
         <v>519</v>
@@ -1237,31 +1237,31 @@
     </row>
     <row r="143">
       <c r="B143" s="7">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C143" s="8">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" s="7">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C144" s="8">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="7">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C145" s="8">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="7">
-        <v>43</v>
+        <v>273</v>
       </c>
       <c r="C146" s="8">
         <v>525</v>
@@ -1269,23 +1269,23 @@
     </row>
     <row r="147">
       <c r="B147" s="7">
-        <v>273</v>
+        <v>43</v>
       </c>
       <c r="C147" s="8">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" s="7">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C148" s="8">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="7">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C149" s="8">
         <v>527</v>
@@ -1293,31 +1293,31 @@
     </row>
     <row r="150">
       <c r="B150" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C150" s="8">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="7">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C151" s="8">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="7">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C152" s="8">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="7">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="C153" s="8">
         <v>530</v>
@@ -1325,23 +1325,23 @@
     </row>
     <row r="154">
       <c r="B154" s="7">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C154" s="8">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="7">
-        <v>311</v>
+        <v>176</v>
       </c>
       <c r="C155" s="8">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="C156" s="8">
         <v>533</v>
@@ -1349,23 +1349,23 @@
     </row>
     <row r="157">
       <c r="B157" s="7">
-        <v>53</v>
+        <v>242</v>
       </c>
       <c r="C157" s="8">
-        <v>533</v>
+        <v>554</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7">
-        <v>242</v>
+        <v>366</v>
       </c>
       <c r="C158" s="8">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7">
-        <v>366</v>
+        <v>246</v>
       </c>
       <c r="C159" s="8">
         <v>555</v>
@@ -1373,15 +1373,15 @@
     </row>
     <row r="160">
       <c r="B160" s="7">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="C160" s="8">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="C161" s="8">
         <v>556</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="162">
       <c r="B162" s="7">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="C162" s="8">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="163">
@@ -1400,7 +1400,7 @@
         <v>312</v>
       </c>
       <c r="C163" s="8">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="164">
@@ -1408,20 +1408,20 @@
         <v>312</v>
       </c>
       <c r="C164" s="8">
-        <v>558</v>
+        <v>568</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="7">
-        <v>312</v>
+        <v>88</v>
       </c>
       <c r="C165" s="8">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C166" s="8">
         <v>569</v>
@@ -1429,42 +1429,42 @@
     </row>
     <row r="167">
       <c r="B167" s="7">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="C167" s="8">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C168" s="8">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="C169" s="8">
-        <v>571</v>
+        <v>713</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7">
-        <v>296</v>
+        <v>469</v>
       </c>
       <c r="C170" s="8">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="7">
-        <v>469</v>
+        <v>117</v>
       </c>
       <c r="C171" s="8">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="172">
@@ -1472,68 +1472,68 @@
         <v>117</v>
       </c>
       <c r="C172" s="8">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="7">
-        <v>117</v>
+        <v>468</v>
       </c>
       <c r="C173" s="8">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="7">
-        <v>468</v>
+        <v>362</v>
       </c>
       <c r="C174" s="8">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7">
-        <v>362</v>
+        <v>313</v>
       </c>
       <c r="C175" s="8">
-        <v>708</v>
+        <v>469</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="7">
-        <v>313</v>
+        <v>71</v>
       </c>
       <c r="C176" s="8">
-        <v>469</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="7">
-        <v>71</v>
+        <v>444</v>
       </c>
       <c r="C177" s="8">
-        <v>44</v>
+        <v>449</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="7">
-        <v>444</v>
+        <v>328</v>
       </c>
       <c r="C178" s="8">
-        <v>449</v>
+        <v>516</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="7">
-        <v>328</v>
+        <v>183</v>
       </c>
       <c r="C179" s="8">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C180" s="8">
         <v>518</v>
@@ -1541,15 +1541,15 @@
     </row>
     <row r="181">
       <c r="B181" s="7">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C181" s="8">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="7">
-        <v>312</v>
+        <v>486</v>
       </c>
       <c r="C182" s="8">
         <v>521</v>
@@ -1560,12 +1560,12 @@
         <v>486</v>
       </c>
       <c r="C183" s="8">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="7">
-        <v>486</v>
+        <v>313</v>
       </c>
       <c r="C184" s="8">
         <v>522</v>
@@ -1573,15 +1573,15 @@
     </row>
     <row r="185">
       <c r="B185" s="7">
-        <v>313</v>
+        <v>250</v>
       </c>
       <c r="C185" s="8">
-        <v>522</v>
+        <v>572</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" s="7">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="C186" s="8">
         <v>572</v>
@@ -1589,15 +1589,15 @@
     </row>
     <row r="187">
       <c r="B187" s="7">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="C187" s="8">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="7">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="C188" s="8">
         <v>573</v>
@@ -1605,23 +1605,23 @@
     </row>
     <row r="189">
       <c r="B189" s="7">
-        <v>328</v>
+        <v>461</v>
       </c>
       <c r="C189" s="8">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" s="7">
-        <v>461</v>
+        <v>95</v>
       </c>
       <c r="C190" s="8">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" s="7">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="C191" s="8">
         <v>577</v>
@@ -1629,15 +1629,15 @@
     </row>
     <row r="192">
       <c r="B192" s="7">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C192" s="8">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" s="7">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="C193" s="8">
         <v>578</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="194">
       <c r="B194" s="7">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C194" s="8">
         <v>578</v>
@@ -1653,15 +1653,15 @@
     </row>
     <row r="195">
       <c r="B195" s="7">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="C195" s="8">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="196">
       <c r="B196" s="7">
-        <v>218</v>
+        <v>417</v>
       </c>
       <c r="C196" s="8">
         <v>579</v>
@@ -1669,39 +1669,39 @@
     </row>
     <row r="197">
       <c r="B197" s="7">
-        <v>417</v>
+        <v>196</v>
       </c>
       <c r="C197" s="8">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C198" s="8">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" s="7">
-        <v>195</v>
+        <v>407</v>
       </c>
       <c r="C199" s="8">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="7">
-        <v>407</v>
+        <v>126</v>
       </c>
       <c r="C200" s="8">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C201" s="8">
         <v>583</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="202">
       <c r="B202" s="7">
-        <v>127</v>
+        <v>429</v>
       </c>
       <c r="C202" s="8">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="203">
@@ -1720,15 +1720,15 @@
         <v>429</v>
       </c>
       <c r="C203" s="8">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" s="7">
-        <v>429</v>
+        <v>120</v>
       </c>
       <c r="C204" s="8">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="205">
@@ -1736,20 +1736,20 @@
         <v>120</v>
       </c>
       <c r="C205" s="8">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="7">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C206" s="8">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="7">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="C207" s="8">
         <v>595</v>
@@ -1757,15 +1757,15 @@
     </row>
     <row r="208">
       <c r="B208" s="7">
-        <v>49</v>
+        <v>384</v>
       </c>
       <c r="C208" s="8">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="7">
-        <v>384</v>
+        <v>49</v>
       </c>
       <c r="C209" s="8">
         <v>596</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="210">
       <c r="B210" s="7">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C210" s="8">
         <v>596</v>
@@ -1781,15 +1781,15 @@
     </row>
     <row r="211">
       <c r="B211" s="7">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C211" s="8">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C212" s="8">
         <v>599</v>
@@ -1797,15 +1797,15 @@
     </row>
     <row r="213">
       <c r="B213" s="7">
-        <v>10</v>
+        <v>311</v>
       </c>
       <c r="C213" s="8">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="7">
-        <v>311</v>
+        <v>10</v>
       </c>
       <c r="C214" s="8">
         <v>601</v>
@@ -1813,15 +1813,15 @@
     </row>
     <row r="215">
       <c r="B215" s="7">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="C215" s="8">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="7">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="C216" s="8">
         <v>602</v>
@@ -1829,15 +1829,15 @@
     </row>
     <row r="217">
       <c r="B217" s="7">
-        <v>10</v>
+        <v>314</v>
       </c>
       <c r="C217" s="8">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="7">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="C218" s="8">
         <v>609</v>
@@ -1845,15 +1845,15 @@
     </row>
     <row r="219">
       <c r="B219" s="7">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="C219" s="8">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" s="7">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="C220" s="8">
         <v>610</v>
@@ -1861,34 +1861,34 @@
     </row>
     <row r="221">
       <c r="B221" s="7">
-        <v>35</v>
+        <v>313</v>
       </c>
       <c r="C221" s="8">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="7">
-        <v>313</v>
+        <v>135</v>
       </c>
       <c r="C222" s="8">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="7">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="C223" s="8">
-        <v>612</v>
+        <v>629</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="7">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C224" s="8">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="225">
@@ -1896,28 +1896,28 @@
         <v>145</v>
       </c>
       <c r="C225" s="8">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="7">
-        <v>145</v>
+        <v>487</v>
       </c>
       <c r="C226" s="8">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="7">
-        <v>487</v>
+        <v>196</v>
       </c>
       <c r="C227" s="8">
-        <v>633</v>
+        <v>260</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C228" s="8">
         <v>260</v>
@@ -1925,15 +1925,15 @@
     </row>
     <row r="229">
       <c r="B229" s="7">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="C229" s="8">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="7">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C230" s="8">
         <v>264</v>
@@ -1941,26 +1941,26 @@
     </row>
     <row r="231">
       <c r="B231" s="7">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="C231" s="8">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="7">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C232" s="8">
-        <v>272</v>
+        <v>294</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="7">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C233" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="234">
@@ -1968,111 +1968,111 @@
         <v>328</v>
       </c>
       <c r="C234" s="8">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="7">
-        <v>328</v>
+        <v>439</v>
       </c>
       <c r="C235" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="7">
-        <v>439</v>
+        <v>33</v>
       </c>
       <c r="C236" s="8">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="7">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C237" s="8">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="7">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C238" s="8">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="7">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C239" s="8">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="7">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C240" s="8">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C241" s="8">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="7">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="C242" s="8">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C243" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="7">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="C244" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C245" s="8">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="7">
-        <v>238</v>
+        <v>38</v>
       </c>
       <c r="C246" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C247" s="8">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="248">
@@ -2080,39 +2080,39 @@
         <v>38</v>
       </c>
       <c r="C248" s="8">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="7">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="C249" s="8">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="7">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="C250" s="8">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="7">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="C251" s="8">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="7">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="C252" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="253">
@@ -2120,172 +2120,172 @@
         <v>312</v>
       </c>
       <c r="C253" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="7">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="C254" s="8">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" s="7">
-        <v>312</v>
+        <v>210</v>
       </c>
       <c r="C255" s="8">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="7">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="C256" s="8">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="7">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C257" s="8">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="7">
-        <v>196</v>
+        <v>417</v>
       </c>
       <c r="C258" s="8">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="7">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C259" s="8">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="7">
-        <v>417</v>
+        <v>125</v>
       </c>
       <c r="C260" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="7">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="C261" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="7">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C262" s="8">
-        <v>379</v>
+        <v>225</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="7">
-        <v>69</v>
+        <v>368</v>
       </c>
       <c r="C263" s="8">
-        <v>379</v>
+        <v>115</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="7">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C264" s="8">
-        <v>225</v>
+        <v>673</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="7">
-        <v>368</v>
+        <v>177</v>
       </c>
       <c r="C265" s="8">
-        <v>115</v>
+        <v>674</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="7">
-        <v>177</v>
+        <v>444</v>
       </c>
       <c r="C266" s="8">
-        <v>673</v>
+        <v>518</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="7">
-        <v>177</v>
+        <v>485</v>
       </c>
       <c r="C267" s="8">
-        <v>674</v>
+        <v>250</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="7">
-        <v>444</v>
+        <v>311</v>
       </c>
       <c r="C268" s="8">
-        <v>518</v>
+        <v>714</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="7">
-        <v>485</v>
+        <v>50</v>
       </c>
       <c r="C269" s="8">
-        <v>250</v>
+        <v>55</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="7">
-        <v>311</v>
+        <v>110</v>
       </c>
       <c r="C270" s="8">
-        <v>714</v>
+        <v>96</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="7">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="C271" s="8">
-        <v>55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C272" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" s="7">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C273" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="7">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="C274" s="8">
         <v>98</v>
@@ -2293,55 +2293,55 @@
     </row>
     <row r="275">
       <c r="B275" s="7">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C275" s="8">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" s="7">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C276" s="8">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="7">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C277" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="7">
-        <v>59</v>
+        <v>271</v>
       </c>
       <c r="C278" s="8">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" s="7">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="C279" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" s="7">
-        <v>271</v>
+        <v>127</v>
       </c>
       <c r="C280" s="8">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" s="7">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C281" s="8">
         <v>111</v>
@@ -2349,143 +2349,143 @@
     </row>
     <row r="282">
       <c r="B282" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C282" s="8">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="7">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C283" s="8">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" s="7">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C284" s="8">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" s="7">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C285" s="8">
-        <v>113</v>
+        <v>142</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" s="7">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C286" s="8">
-        <v>117</v>
+        <v>216</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" s="7">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C287" s="8">
-        <v>142</v>
+        <v>217</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" s="7">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="C288" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" s="7">
-        <v>166</v>
+        <v>445</v>
       </c>
       <c r="C289" s="8">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" s="7">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="C290" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="7">
-        <v>445</v>
+        <v>220</v>
       </c>
       <c r="C291" s="8">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" s="7">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="C292" s="8">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" s="7">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C293" s="8">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="7">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="C294" s="8">
-        <v>224</v>
+        <v>262</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" s="7">
-        <v>245</v>
+        <v>522</v>
       </c>
       <c r="C295" s="8">
-        <v>227</v>
+        <v>266</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" s="7">
-        <v>38</v>
+        <v>522</v>
       </c>
       <c r="C296" s="8">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" s="7">
-        <v>522</v>
+        <v>201</v>
       </c>
       <c r="C297" s="8">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" s="7">
-        <v>522</v>
+        <v>200</v>
       </c>
       <c r="C298" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C299" s="8">
         <v>270</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="300">
       <c r="B300" s="7">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="C300" s="8">
         <v>270</v>
@@ -2501,18 +2501,18 @@
     </row>
     <row r="301">
       <c r="B301" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C301" s="8">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="302">
       <c r="B302" s="7">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="C302" s="8">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="303">
@@ -2520,55 +2520,55 @@
         <v>209</v>
       </c>
       <c r="C303" s="8">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C304" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="305">
       <c r="B305" s="7">
-        <v>209</v>
+        <v>313</v>
       </c>
       <c r="C305" s="8">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" s="7">
-        <v>209</v>
+        <v>36</v>
       </c>
       <c r="C306" s="8">
-        <v>289</v>
+        <v>318</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" s="7">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="C307" s="8">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" s="7">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C308" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" s="7">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C309" s="8">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="310">
@@ -2576,79 +2576,79 @@
         <v>53</v>
       </c>
       <c r="C310" s="8">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" s="7">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C311" s="8">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" s="7">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C312" s="8">
-        <v>324</v>
+        <v>342</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" s="7">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="C313" s="8">
-        <v>340</v>
+        <v>358</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" s="7">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="C314" s="8">
-        <v>342</v>
+        <v>361</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" s="7">
-        <v>123</v>
+        <v>384</v>
       </c>
       <c r="C315" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" s="7">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="C316" s="8">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" s="7">
-        <v>384</v>
+        <v>125</v>
       </c>
       <c r="C317" s="8">
-        <v>363</v>
+        <v>382</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" s="7">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="C318" s="8">
-        <v>369</v>
+        <v>382</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" s="7">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C319" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="320">
@@ -2656,7 +2656,7 @@
         <v>69</v>
       </c>
       <c r="C320" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="321">
@@ -2664,7 +2664,7 @@
         <v>106</v>
       </c>
       <c r="C321" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="322">
@@ -2672,15 +2672,15 @@
         <v>69</v>
       </c>
       <c r="C322" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="323">
       <c r="B323" s="7">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="C323" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="324">
@@ -2688,7 +2688,7 @@
         <v>69</v>
       </c>
       <c r="C324" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="325">
@@ -2696,7 +2696,7 @@
         <v>49</v>
       </c>
       <c r="C325" s="8">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="326">
@@ -2704,28 +2704,28 @@
         <v>69</v>
       </c>
       <c r="C326" s="8">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="327">
       <c r="B327" s="7">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C327" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="328">
       <c r="B328" s="7">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C328" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="329">
       <c r="B329" s="7">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C329" s="8">
         <v>392</v>
@@ -2733,39 +2733,39 @@
     </row>
     <row r="330">
       <c r="B330" s="7">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C330" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="331">
       <c r="B331" s="7">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C331" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="332">
       <c r="B332" s="7">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C332" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="333">
       <c r="B333" s="7">
-        <v>123</v>
+        <v>429</v>
       </c>
       <c r="C333" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="334">
       <c r="B334" s="7">
-        <v>119</v>
+        <v>489</v>
       </c>
       <c r="C334" s="8">
         <v>395</v>
@@ -2773,23 +2773,23 @@
     </row>
     <row r="335">
       <c r="B335" s="7">
-        <v>429</v>
+        <v>27</v>
       </c>
       <c r="C335" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="336">
       <c r="B336" s="7">
-        <v>489</v>
+        <v>323</v>
       </c>
       <c r="C336" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="337">
       <c r="B337" s="7">
-        <v>27</v>
+        <v>324</v>
       </c>
       <c r="C337" s="8">
         <v>397</v>
@@ -2797,7 +2797,7 @@
     </row>
     <row r="338">
       <c r="B338" s="7">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="C338" s="8">
         <v>397</v>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="339">
       <c r="B339" s="7">
-        <v>324</v>
+        <v>59</v>
       </c>
       <c r="C339" s="8">
         <v>397</v>
@@ -2813,42 +2813,42 @@
     </row>
     <row r="340">
       <c r="B340" s="7">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="C340" s="8">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="341">
       <c r="B341" s="7">
-        <v>59</v>
+        <v>221</v>
       </c>
       <c r="C341" s="8">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="342">
       <c r="B342" s="7">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="C342" s="8">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="343">
       <c r="B343" s="7">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C343" s="8">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="344">
       <c r="B344" s="7">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C344" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="345">
@@ -2856,36 +2856,36 @@
         <v>163</v>
       </c>
       <c r="C345" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="346">
       <c r="B346" s="7">
-        <v>89</v>
+        <v>328</v>
       </c>
       <c r="C346" s="8">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="347">
       <c r="B347" s="7">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C347" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="348">
       <c r="B348" s="7">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C348" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="349">
       <c r="B349" s="7">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="C349" s="8">
         <v>413</v>
@@ -2893,34 +2893,34 @@
     </row>
     <row r="350">
       <c r="B350" s="7">
-        <v>338</v>
+        <v>248</v>
       </c>
       <c r="C350" s="8">
-        <v>413</v>
+        <v>442</v>
       </c>
     </row>
     <row r="351">
       <c r="B351" s="7">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C351" s="8">
-        <v>413</v>
+        <v>639</v>
       </c>
     </row>
     <row r="352">
       <c r="B352" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C352" s="8">
-        <v>442</v>
+        <v>639</v>
       </c>
     </row>
     <row r="353">
       <c r="B353" s="7">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C353" s="8">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="354">
@@ -2928,36 +2928,36 @@
         <v>247</v>
       </c>
       <c r="C354" s="8">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="355">
       <c r="B355" s="7">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="C355" s="8">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="356">
       <c r="B356" s="7">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="C356" s="8">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="357">
       <c r="B357" s="7">
-        <v>328</v>
+        <v>384</v>
       </c>
       <c r="C357" s="8">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="358">
       <c r="B358" s="7">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="C358" s="8">
         <v>644</v>
@@ -2965,23 +2965,23 @@
     </row>
     <row r="359">
       <c r="B359" s="7">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="C359" s="8">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="360">
       <c r="B360" s="7">
-        <v>312</v>
+        <v>183</v>
       </c>
       <c r="C360" s="8">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="361">
       <c r="B361" s="7">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="C361" s="8">
         <v>645</v>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="362">
       <c r="B362" s="7">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C362" s="8">
         <v>645</v>
@@ -2997,10 +2997,10 @@
     </row>
     <row r="363">
       <c r="B363" s="7">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="C363" s="8">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="364">
@@ -3008,23 +3008,23 @@
         <v>123</v>
       </c>
       <c r="C364" s="8">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="365">
       <c r="B365" s="7">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="C365" s="8">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="366">
       <c r="B366" s="7">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="C366" s="8">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="367">
@@ -3032,36 +3032,36 @@
         <v>123</v>
       </c>
       <c r="C367" s="8">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="368">
       <c r="B368" s="7">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="C368" s="8">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="369">
       <c r="B369" s="7">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C369" s="8">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="370">
       <c r="B370" s="7">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C370" s="8">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="371">
       <c r="B371" s="7">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C371" s="8">
         <v>649</v>
@@ -3072,7 +3072,7 @@
         <v>123</v>
       </c>
       <c r="C372" s="8">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="373">
@@ -3080,12 +3080,12 @@
         <v>105</v>
       </c>
       <c r="C373" s="8">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="374">
       <c r="B374" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C374" s="8">
         <v>650</v>
@@ -3093,55 +3093,55 @@
     </row>
     <row r="375">
       <c r="B375" s="7">
-        <v>105</v>
+        <v>339</v>
       </c>
       <c r="C375" s="8">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="376">
       <c r="B376" s="7">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C376" s="8">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="377">
       <c r="B377" s="7">
-        <v>339</v>
+        <v>64</v>
       </c>
       <c r="C377" s="8">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="378">
       <c r="B378" s="7">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C378" s="8">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="379">
       <c r="B379" s="7">
-        <v>64</v>
+        <v>274</v>
       </c>
       <c r="C379" s="8">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="380">
       <c r="B380" s="7">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="C380" s="8">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="381">
       <c r="B381" s="7">
-        <v>274</v>
+        <v>120</v>
       </c>
       <c r="C381" s="8">
         <v>654</v>
@@ -3149,26 +3149,26 @@
     </row>
     <row r="382">
       <c r="B382" s="7">
-        <v>64</v>
+        <v>459</v>
       </c>
       <c r="C382" s="8">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="383">
       <c r="B383" s="7">
-        <v>120</v>
+        <v>231</v>
       </c>
       <c r="C383" s="8">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="384">
       <c r="B384" s="7">
-        <v>459</v>
+        <v>127</v>
       </c>
       <c r="C384" s="8">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="385">
@@ -3176,15 +3176,15 @@
         <v>231</v>
       </c>
       <c r="C385" s="8">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="386">
       <c r="B386" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C386" s="8">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="387">
@@ -3192,167 +3192,167 @@
         <v>231</v>
       </c>
       <c r="C387" s="8">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="388">
       <c r="B388" s="7">
-        <v>126</v>
+        <v>286</v>
       </c>
       <c r="C388" s="8">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="389">
       <c r="B389" s="7">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="C389" s="8">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="390">
       <c r="B390" s="7">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C390" s="8">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="391">
       <c r="B391" s="7">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="C391" s="8">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="392">
       <c r="B392" s="7">
-        <v>274</v>
+        <v>59</v>
       </c>
       <c r="C392" s="8">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="393">
       <c r="B393" s="7">
-        <v>229</v>
+        <v>65</v>
       </c>
       <c r="C393" s="8">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="394">
       <c r="B394" s="7">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C394" s="8">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="395">
       <c r="B395" s="7">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C395" s="8">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="396">
       <c r="B396" s="7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C396" s="8">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="397">
       <c r="B397" s="7">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="C397" s="8">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="398">
       <c r="B398" s="7">
-        <v>60</v>
+        <v>523</v>
       </c>
       <c r="C398" s="8">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="399">
       <c r="B399" s="7">
-        <v>60</v>
+        <v>501</v>
       </c>
       <c r="C399" s="8">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="400">
       <c r="B400" s="7">
-        <v>523</v>
+        <v>169</v>
       </c>
       <c r="C400" s="8">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="401">
       <c r="B401" s="7">
-        <v>501</v>
+        <v>59</v>
       </c>
       <c r="C401" s="8">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="402">
       <c r="B402" s="7">
-        <v>169</v>
+        <v>10</v>
       </c>
       <c r="C402" s="8">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="403">
       <c r="B403" s="7">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="C403" s="8">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="404">
       <c r="B404" s="7">
-        <v>10</v>
+        <v>524</v>
       </c>
       <c r="C404" s="8">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="405">
       <c r="B405" s="7">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="C405" s="8">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="406">
       <c r="B406" s="7">
-        <v>524</v>
+        <v>50</v>
       </c>
       <c r="C406" s="8">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="407">
       <c r="B407" s="7">
-        <v>37</v>
+        <v>209</v>
       </c>
       <c r="C407" s="8">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="408">
@@ -3360,87 +3360,87 @@
         <v>23</v>
       </c>
       <c r="C408" s="8">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="409">
       <c r="B409" s="7">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C409" s="8">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="410">
       <c r="B410" s="7">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="C410" s="8">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="411">
       <c r="B411" s="7">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="C411" s="8">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="412">
       <c r="B412" s="7">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="C412" s="8">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="413">
       <c r="B413" s="7">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="C413" s="8">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="414">
       <c r="B414" s="7">
-        <v>166</v>
+        <v>525</v>
       </c>
       <c r="C414" s="8">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="415">
       <c r="B415" s="7">
-        <v>445</v>
+        <v>55</v>
       </c>
       <c r="C415" s="8">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="416">
       <c r="B416" s="7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C416" s="8">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="417">
       <c r="B417" s="7">
-        <v>525</v>
+        <v>231</v>
       </c>
       <c r="C417" s="8">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="418">
       <c r="B418" s="7">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C418" s="8">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="419">
@@ -3448,111 +3448,111 @@
         <v>60</v>
       </c>
       <c r="C419" s="8">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="420">
       <c r="B420" s="7">
-        <v>231</v>
+        <v>459</v>
       </c>
       <c r="C420" s="8">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="421">
       <c r="B421" s="7">
-        <v>97</v>
+        <v>244</v>
       </c>
       <c r="C421" s="8">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="422">
       <c r="B422" s="7">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C422" s="8">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="423">
       <c r="B423" s="7">
-        <v>459</v>
+        <v>204</v>
       </c>
       <c r="C423" s="8">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="424">
       <c r="B424" s="7">
-        <v>244</v>
+        <v>363</v>
       </c>
       <c r="C424" s="8">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="425">
       <c r="B425" s="7">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C425" s="8">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="426">
       <c r="B426" s="7">
-        <v>204</v>
+        <v>328</v>
       </c>
       <c r="C426" s="8">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="427">
       <c r="B427" s="7">
-        <v>363</v>
+        <v>183</v>
       </c>
       <c r="C427" s="8">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="428">
       <c r="B428" s="7">
-        <v>59</v>
+        <v>328</v>
       </c>
       <c r="C428" s="8">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="429">
       <c r="B429" s="7">
-        <v>328</v>
+        <v>182</v>
       </c>
       <c r="C429" s="8">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="430">
       <c r="B430" s="7">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C430" s="8">
-        <v>699</v>
+        <v>157</v>
       </c>
     </row>
     <row r="431">
       <c r="B431" s="7">
-        <v>328</v>
+        <v>54</v>
       </c>
       <c r="C431" s="8">
-        <v>700</v>
+        <v>157</v>
       </c>
     </row>
     <row r="432">
       <c r="B432" s="7">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="C432" s="8">
-        <v>700</v>
+        <v>294</v>
       </c>
     </row>
     <row r="433">
@@ -3560,39 +3560,39 @@
         <v>152</v>
       </c>
       <c r="C433" s="8">
-        <v>157</v>
+        <v>552</v>
       </c>
     </row>
     <row r="434">
       <c r="B434" s="7">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C434" s="8">
-        <v>157</v>
+        <v>552</v>
       </c>
     </row>
     <row r="435">
       <c r="B435" s="7">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C435" s="8">
-        <v>294</v>
+        <v>726</v>
       </c>
     </row>
     <row r="436">
       <c r="B436" s="7">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C436" s="8">
-        <v>552</v>
+        <v>727</v>
       </c>
     </row>
     <row r="437">
       <c r="B437" s="7">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C437" s="8">
-        <v>552</v>
+        <v>728</v>
       </c>
     </row>
     <row r="438">
@@ -3600,63 +3600,63 @@
         <v>22</v>
       </c>
       <c r="C438" s="8">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="439">
       <c r="B439" s="7">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="C439" s="8">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="440">
       <c r="B440" s="7">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="C440" s="8">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="441">
       <c r="B441" s="7">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="C441" s="8">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="442">
       <c r="B442" s="7">
-        <v>227</v>
+        <v>23</v>
       </c>
       <c r="C442" s="8">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="443">
       <c r="B443" s="7">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="C443" s="8">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="444">
       <c r="B444" s="7">
-        <v>234</v>
+        <v>23</v>
       </c>
       <c r="C444" s="8">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="445">
       <c r="B445" s="7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C445" s="8">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="446">
@@ -3664,7 +3664,7 @@
         <v>22</v>
       </c>
       <c r="C446" s="8">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="447">
@@ -3672,7 +3672,7 @@
         <v>23</v>
       </c>
       <c r="C447" s="8">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="448">
@@ -3680,55 +3680,55 @@
         <v>22</v>
       </c>
       <c r="C448" s="8">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="449">
       <c r="B449" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C449" s="8">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="450">
       <c r="B450" s="7">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="C450" s="8">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="451">
       <c r="B451" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C451" s="8">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="452">
       <c r="B452" s="7">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="C452" s="8">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="453">
       <c r="B453" s="7">
-        <v>209</v>
+        <v>23</v>
       </c>
       <c r="C453" s="8">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="454">
       <c r="B454" s="7">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C454" s="8">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="455">
@@ -3736,7 +3736,7 @@
         <v>209</v>
       </c>
       <c r="C455" s="8">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="456">
@@ -3744,31 +3744,31 @@
         <v>23</v>
       </c>
       <c r="C456" s="8">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="457">
       <c r="B457" s="7">
-        <v>16</v>
+        <v>359</v>
       </c>
       <c r="C457" s="8">
-        <v>737</v>
+        <v>445</v>
       </c>
     </row>
     <row r="458">
       <c r="B458" s="7">
-        <v>209</v>
+        <v>98</v>
       </c>
       <c r="C458" s="8">
-        <v>737</v>
+        <v>445</v>
       </c>
     </row>
     <row r="459">
       <c r="B459" s="7">
-        <v>23</v>
+        <v>313</v>
       </c>
       <c r="C459" s="8">
-        <v>737</v>
+        <v>446</v>
       </c>
     </row>
     <row r="460">
@@ -3776,55 +3776,55 @@
         <v>359</v>
       </c>
       <c r="C460" s="8">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="461">
       <c r="B461" s="7">
-        <v>98</v>
+        <v>313</v>
       </c>
       <c r="C461" s="8">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="462">
       <c r="B462" s="7">
-        <v>313</v>
+        <v>214</v>
       </c>
       <c r="C462" s="8">
-        <v>446</v>
+        <v>714</v>
       </c>
     </row>
     <row r="463">
       <c r="B463" s="7">
-        <v>359</v>
+        <v>216</v>
       </c>
       <c r="C463" s="8">
-        <v>447</v>
+        <v>715</v>
       </c>
     </row>
     <row r="464">
       <c r="B464" s="7">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C464" s="8">
-        <v>447</v>
+        <v>715</v>
       </c>
     </row>
     <row r="465">
       <c r="B465" s="7">
-        <v>214</v>
+        <v>311</v>
       </c>
       <c r="C465" s="8">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="466">
       <c r="B466" s="7">
-        <v>216</v>
+        <v>311</v>
       </c>
       <c r="C466" s="8">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="467">
@@ -3832,39 +3832,39 @@
         <v>311</v>
       </c>
       <c r="C467" s="8">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="468">
       <c r="B468" s="7">
-        <v>311</v>
+        <v>22</v>
       </c>
       <c r="C468" s="8">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="469">
       <c r="B469" s="7">
-        <v>311</v>
+        <v>22</v>
       </c>
       <c r="C469" s="8">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="470">
       <c r="B470" s="7">
-        <v>311</v>
+        <v>22</v>
       </c>
       <c r="C470" s="8">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="471">
       <c r="B471" s="7">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C471" s="8">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="472">
@@ -3872,247 +3872,247 @@
         <v>22</v>
       </c>
       <c r="C472" s="8">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="473">
       <c r="B473" s="7">
-        <v>22</v>
+        <v>328</v>
       </c>
       <c r="C473" s="8">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="474">
       <c r="B474" s="7">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C474" s="8">
-        <v>723</v>
+        <v>25</v>
       </c>
     </row>
     <row r="475">
       <c r="B475" s="7">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C475" s="8">
-        <v>724</v>
+        <v>477</v>
       </c>
     </row>
     <row r="476">
       <c r="B476" s="7">
-        <v>328</v>
+        <v>177</v>
       </c>
       <c r="C476" s="8">
-        <v>725</v>
+        <v>520</v>
       </c>
     </row>
     <row r="477">
       <c r="B477" s="7">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C477" s="8">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="478">
       <c r="B478" s="7">
+        <v>118</v>
+      </c>
+      <c r="C478" s="8">
         <v>14</v>
-      </c>
-      <c r="C478" s="8">
-        <v>477</v>
       </c>
     </row>
     <row r="479">
       <c r="B479" s="7">
-        <v>177</v>
+        <v>16</v>
       </c>
       <c r="C479" s="8">
-        <v>520</v>
+        <v>15</v>
       </c>
     </row>
     <row r="480">
       <c r="B480" s="7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C480" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="481">
       <c r="B481" s="7">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="C481" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="482">
       <c r="B482" s="7">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C482" s="8">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="483">
       <c r="B483" s="7">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C483" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="484">
       <c r="B484" s="7">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C484" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="485">
       <c r="B485" s="7">
-        <v>26</v>
+        <v>527</v>
       </c>
       <c r="C485" s="8">
-        <v>22</v>
+        <v>764</v>
       </c>
     </row>
     <row r="486">
       <c r="B486" s="7">
-        <v>56</v>
+        <v>509</v>
       </c>
       <c r="C486" s="8">
-        <v>30</v>
+        <v>764</v>
       </c>
     </row>
     <row r="487">
       <c r="B487" s="7">
-        <v>35</v>
+        <v>458</v>
       </c>
       <c r="C487" s="8">
-        <v>30</v>
+        <v>765</v>
       </c>
     </row>
     <row r="488">
       <c r="B488" s="7">
-        <v>527</v>
+        <v>137</v>
       </c>
       <c r="C488" s="8">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="489">
       <c r="B489" s="7">
-        <v>509</v>
+        <v>62</v>
       </c>
       <c r="C489" s="8">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="490">
       <c r="B490" s="7">
-        <v>458</v>
+        <v>164</v>
       </c>
       <c r="C490" s="8">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="491">
       <c r="B491" s="7">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C491" s="8">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="492">
       <c r="B492" s="7">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C492" s="8">
-        <v>763</v>
+        <v>775</v>
       </c>
     </row>
     <row r="493">
       <c r="B493" s="7">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="C493" s="8">
-        <v>767</v>
+        <v>775</v>
       </c>
     </row>
     <row r="494">
       <c r="B494" s="7">
-        <v>164</v>
+        <v>324</v>
       </c>
       <c r="C494" s="8">
-        <v>768</v>
+        <v>779</v>
       </c>
     </row>
     <row r="495">
       <c r="B495" s="7">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="C495" s="8">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="496">
       <c r="B496" s="7">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="C496" s="8">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="497">
       <c r="B497" s="7">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C497" s="8">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="498">
       <c r="B498" s="7">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="C498" s="8">
-        <v>779</v>
+        <v>738</v>
       </c>
     </row>
     <row r="499">
       <c r="B499" s="7">
-        <v>117</v>
+        <v>314</v>
       </c>
       <c r="C499" s="8">
-        <v>779</v>
+        <v>745</v>
       </c>
     </row>
     <row r="500">
       <c r="B500" s="7">
-        <v>312</v>
+        <v>123</v>
       </c>
       <c r="C500" s="8">
-        <v>780</v>
+        <v>745</v>
       </c>
     </row>
     <row r="501">
       <c r="B501" s="7">
-        <v>36</v>
+        <v>227</v>
       </c>
       <c r="C501" s="8">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="502">
       <c r="B502" s="7">
-        <v>314</v>
+        <v>227</v>
       </c>
       <c r="C502" s="8">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="503">
@@ -4120,36 +4120,36 @@
         <v>123</v>
       </c>
       <c r="C503" s="8">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="504">
       <c r="B504" s="7">
-        <v>227</v>
+        <v>24</v>
       </c>
       <c r="C504" s="8">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="505">
       <c r="B505" s="7">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="C505" s="8">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="506">
       <c r="B506" s="7">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="C506" s="8">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="507">
       <c r="B507" s="7">
-        <v>24</v>
+        <v>312</v>
       </c>
       <c r="C507" s="8">
         <v>741</v>
@@ -4157,26 +4157,26 @@
     </row>
     <row r="508">
       <c r="B508" s="7">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C508" s="8">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="509">
       <c r="B509" s="7">
-        <v>23</v>
+        <v>312</v>
       </c>
       <c r="C509" s="8">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="510">
       <c r="B510" s="7">
-        <v>312</v>
+        <v>23</v>
       </c>
       <c r="C510" s="8">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="511">
@@ -4184,23 +4184,23 @@
         <v>49</v>
       </c>
       <c r="C511" s="8">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="512">
       <c r="B512" s="7">
-        <v>312</v>
+        <v>428</v>
       </c>
       <c r="C512" s="8">
-        <v>742</v>
+        <v>747</v>
       </c>
     </row>
     <row r="513">
       <c r="B513" s="7">
-        <v>23</v>
+        <v>415</v>
       </c>
       <c r="C513" s="8">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="514">
@@ -4208,68 +4208,68 @@
         <v>49</v>
       </c>
       <c r="C514" s="8">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="515">
       <c r="B515" s="7">
-        <v>428</v>
+        <v>140</v>
       </c>
       <c r="C515" s="8">
-        <v>747</v>
+        <v>658</v>
       </c>
     </row>
     <row r="516">
       <c r="B516" s="7">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="C516" s="8">
-        <v>748</v>
+        <v>659</v>
       </c>
     </row>
     <row r="517">
       <c r="B517" s="7">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="C517" s="8">
-        <v>749</v>
+        <v>660</v>
       </c>
     </row>
     <row r="518">
       <c r="B518" s="7">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="C518" s="8">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="519">
       <c r="B519" s="7">
-        <v>444</v>
+        <v>266</v>
       </c>
       <c r="C519" s="8">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="520">
       <c r="B520" s="7">
-        <v>132</v>
+        <v>262</v>
       </c>
       <c r="C520" s="8">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="521">
       <c r="B521" s="7">
-        <v>365</v>
+        <v>540</v>
       </c>
       <c r="C521" s="8">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="522">
       <c r="B522" s="7">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="C522" s="8">
         <v>661</v>
@@ -4277,55 +4277,55 @@
     </row>
     <row r="523">
       <c r="B523" s="7">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C523" s="8">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="524">
       <c r="B524" s="7">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C524" s="8">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="525">
       <c r="B525" s="7">
-        <v>324</v>
+        <v>561</v>
       </c>
       <c r="C525" s="8">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="526">
       <c r="B526" s="7">
-        <v>287</v>
+        <v>27</v>
       </c>
       <c r="C526" s="8">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="527">
       <c r="B527" s="7">
-        <v>552</v>
+        <v>27</v>
       </c>
       <c r="C527" s="8">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="528">
       <c r="B528" s="7">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="C528" s="8">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="529">
       <c r="B529" s="7">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="C529" s="8">
         <v>665</v>
@@ -4333,10 +4333,10 @@
     </row>
     <row r="530">
       <c r="B530" s="7">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="C530" s="8">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="531">
@@ -4344,207 +4344,439 @@
         <v>141</v>
       </c>
       <c r="C531" s="8">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="532">
       <c r="B532" s="7">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="C532" s="8">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="533">
       <c r="B533" s="7">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="C533" s="8">
-        <v>664</v>
+        <v>674</v>
       </c>
     </row>
     <row r="534">
       <c r="B534" s="7">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="C534" s="8">
-        <v>663</v>
+        <v>332</v>
       </c>
     </row>
     <row r="535">
       <c r="B535" s="7">
-        <v>365</v>
+        <v>64</v>
       </c>
       <c r="C535" s="8">
-        <v>673</v>
+        <v>40</v>
       </c>
     </row>
     <row r="536">
       <c r="B536" s="7">
-        <v>365</v>
+        <v>541</v>
       </c>
       <c r="C536" s="8">
-        <v>674</v>
+        <v>52</v>
       </c>
     </row>
     <row r="537">
       <c r="B537" s="7">
-        <v>365</v>
+        <v>287</v>
       </c>
       <c r="C537" s="8">
-        <v>332</v>
+        <v>131</v>
       </c>
     </row>
     <row r="538">
       <c r="B538" s="7">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="C538" s="8">
-        <v>40</v>
+        <v>131</v>
       </c>
     </row>
     <row r="539">
       <c r="B539" s="7">
-        <v>541</v>
+        <v>35</v>
       </c>
       <c r="C539" s="8">
-        <v>52</v>
+        <v>521</v>
       </c>
     </row>
     <row r="540">
       <c r="B540" s="7">
-        <v>287</v>
+        <v>390</v>
       </c>
       <c r="C540" s="8">
-        <v>131</v>
+        <v>470</v>
       </c>
     </row>
     <row r="541">
       <c r="B541" s="7">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C541" s="8">
-        <v>131</v>
+        <v>470</v>
       </c>
     </row>
     <row r="542">
       <c r="B542" s="7">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="C542" s="8">
-        <v>521</v>
+        <v>471</v>
       </c>
     </row>
     <row r="543">
       <c r="B543" s="7">
-        <v>390</v>
+        <v>485</v>
       </c>
       <c r="C543" s="8">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="544">
       <c r="B544" s="7">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="C544" s="8">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="545">
       <c r="B545" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C545" s="8">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="546">
       <c r="B546" s="7">
-        <v>485</v>
+        <v>214</v>
       </c>
       <c r="C546" s="8">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="547">
       <c r="B547" s="7">
-        <v>311</v>
+        <v>53</v>
       </c>
       <c r="C547" s="8">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="548">
       <c r="B548" s="7">
-        <v>310</v>
+        <v>252</v>
       </c>
       <c r="C548" s="8">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="549">
       <c r="B549" s="7">
-        <v>214</v>
+        <v>62</v>
       </c>
       <c r="C549" s="8">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="550">
       <c r="B550" s="7">
-        <v>53</v>
+        <v>254</v>
       </c>
       <c r="C550" s="8">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="551">
       <c r="B551" s="7">
-        <v>252</v>
+        <v>17</v>
       </c>
       <c r="C551" s="8">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="552">
       <c r="B552" s="7">
-        <v>62</v>
+        <v>196</v>
       </c>
       <c r="C552" s="8">
-        <v>474</v>
+        <v>483</v>
       </c>
     </row>
     <row r="553">
       <c r="B553" s="7">
-        <v>254</v>
+        <v>59</v>
       </c>
       <c r="C553" s="8">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="554">
       <c r="B554" s="7">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="C554" s="8">
-        <v>482</v>
+        <v>192</v>
       </c>
     </row>
     <row r="555">
       <c r="B555" s="7">
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="C555" s="8">
-        <v>483</v>
+        <v>677</v>
       </c>
     </row>
     <row r="556">
       <c r="B556" s="7">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="C556" s="8">
-        <v>483</v>
+        <v>747</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" s="7">
+        <v>82</v>
+      </c>
+      <c r="C557" s="8">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" s="7">
+        <v>267</v>
+      </c>
+      <c r="C558" s="8">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" s="7">
+        <v>310</v>
+      </c>
+      <c r="C559" s="8">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" s="7">
+        <v>330</v>
+      </c>
+      <c r="C560" s="8">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" s="7">
+        <v>531</v>
+      </c>
+      <c r="C561" s="8">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" s="7">
+        <v>491</v>
+      </c>
+      <c r="C562" s="8">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" s="7">
+        <v>578</v>
+      </c>
+      <c r="C563" s="8">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" s="7">
+        <v>455</v>
+      </c>
+      <c r="C564" s="8">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" s="7">
+        <v>88</v>
+      </c>
+      <c r="C565" s="8">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" s="7">
+        <v>444</v>
+      </c>
+      <c r="C566" s="8">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" s="7">
+        <v>64</v>
+      </c>
+      <c r="C567" s="8">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" s="7">
+        <v>489</v>
+      </c>
+      <c r="C568" s="8">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" s="7">
+        <v>27</v>
+      </c>
+      <c r="C569" s="8">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" s="7">
+        <v>127</v>
+      </c>
+      <c r="C570" s="8">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" s="7">
+        <v>195</v>
+      </c>
+      <c r="C571" s="8">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" s="7">
+        <v>210</v>
+      </c>
+      <c r="C572" s="8">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" s="7">
+        <v>418</v>
+      </c>
+      <c r="C573" s="8">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" s="7">
+        <v>393</v>
+      </c>
+      <c r="C574" s="8">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" s="7">
+        <v>135</v>
+      </c>
+      <c r="C575" s="8">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="B576" s="7">
+        <v>531</v>
+      </c>
+      <c r="C576" s="8">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" s="7">
+        <v>236</v>
+      </c>
+      <c r="C577" s="8">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" s="7">
+        <v>531</v>
+      </c>
+      <c r="C578" s="8">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" s="7">
+        <v>236</v>
+      </c>
+      <c r="C579" s="8">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" s="7">
+        <v>531</v>
+      </c>
+      <c r="C580" s="8">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" s="7">
+        <v>236</v>
+      </c>
+      <c r="C581" s="8">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" s="7">
+        <v>531</v>
+      </c>
+      <c r="C582" s="8">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" s="7">
+        <v>236</v>
+      </c>
+      <c r="C583" s="8">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" s="7">
+        <v>236</v>
+      </c>
+      <c r="C584" s="8">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" s="7">
+        <v>531</v>
+      </c>
+      <c r="C585" s="8">
+        <v>795</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -4779,6 +4779,62 @@
         <v>795</v>
       </c>
     </row>
+    <row r="586">
+      <c r="B586" s="7">
+        <v>23</v>
+      </c>
+      <c r="C586" s="8">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" s="7">
+        <v>23</v>
+      </c>
+      <c r="C587" s="8">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" s="7">
+        <v>163</v>
+      </c>
+      <c r="C588" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" s="7">
+        <v>255</v>
+      </c>
+      <c r="C589" s="8">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" s="7">
+        <v>536</v>
+      </c>
+      <c r="C590" s="8">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" s="7">
+        <v>44</v>
+      </c>
+      <c r="C591" s="8">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" s="7">
+        <v>273</v>
+      </c>
+      <c r="C592" s="8">
+        <v>695</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -1741,7 +1741,7 @@
     </row>
     <row r="206">
       <c r="B206" s="7">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="C206" s="8">
         <v>595</v>
@@ -4835,6 +4835,198 @@
         <v>695</v>
       </c>
     </row>
+    <row r="593">
+      <c r="B593" s="7">
+        <v>359</v>
+      </c>
+      <c r="C593" s="8">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" s="7">
+        <v>48</v>
+      </c>
+      <c r="C594" s="8">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" s="7">
+        <v>19</v>
+      </c>
+      <c r="C595" s="8">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" s="7">
+        <v>70</v>
+      </c>
+      <c r="C596" s="8">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" s="7">
+        <v>439</v>
+      </c>
+      <c r="C597" s="8">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" s="7">
+        <v>106</v>
+      </c>
+      <c r="C598" s="8">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" s="7">
+        <v>49</v>
+      </c>
+      <c r="C599" s="8">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" s="7">
+        <v>580</v>
+      </c>
+      <c r="C600" s="8">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" s="7">
+        <v>448</v>
+      </c>
+      <c r="C601" s="8">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" s="7">
+        <v>559</v>
+      </c>
+      <c r="C602" s="8">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" s="7">
+        <v>559</v>
+      </c>
+      <c r="C603" s="8">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" s="7">
+        <v>522</v>
+      </c>
+      <c r="C604" s="8">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" s="7">
+        <v>522</v>
+      </c>
+      <c r="C605" s="8">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" s="7">
+        <v>126</v>
+      </c>
+      <c r="C606" s="8">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" s="7">
+        <v>127</v>
+      </c>
+      <c r="C607" s="8">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" s="7">
+        <v>141</v>
+      </c>
+      <c r="C608" s="8">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" s="7">
+        <v>141</v>
+      </c>
+      <c r="C609" s="8">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" s="7">
+        <v>207</v>
+      </c>
+      <c r="C610" s="8">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" s="7">
+        <v>205</v>
+      </c>
+      <c r="C611" s="8">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" s="7">
+        <v>141</v>
+      </c>
+      <c r="C612" s="8">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" s="7">
+        <v>359</v>
+      </c>
+      <c r="C613" s="8">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" s="7">
+        <v>359</v>
+      </c>
+      <c r="C614" s="8">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" s="7">
+        <v>169</v>
+      </c>
+      <c r="C615" s="8">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" s="7">
+        <v>472</v>
+      </c>
+      <c r="C616" s="8">
+        <v>621</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -5027,6 +5027,358 @@
         <v>621</v>
       </c>
     </row>
+    <row r="617">
+      <c r="B617" s="7">
+        <v>531</v>
+      </c>
+      <c r="C617" s="8">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" s="7">
+        <v>347</v>
+      </c>
+      <c r="C618" s="8">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" s="7">
+        <v>57</v>
+      </c>
+      <c r="C619" s="8">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" s="7">
+        <v>75</v>
+      </c>
+      <c r="C620" s="8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" s="7">
+        <v>485</v>
+      </c>
+      <c r="C621" s="8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" s="7">
+        <v>366</v>
+      </c>
+      <c r="C622" s="8">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" s="7">
+        <v>246</v>
+      </c>
+      <c r="C623" s="8">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" s="7">
+        <v>49</v>
+      </c>
+      <c r="C624" s="8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" s="7">
+        <v>35</v>
+      </c>
+      <c r="C625" s="8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" s="7">
+        <v>69</v>
+      </c>
+      <c r="C626" s="8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" s="7">
+        <v>135</v>
+      </c>
+      <c r="C627" s="8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" s="7">
+        <v>49</v>
+      </c>
+      <c r="C628" s="8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" s="7">
+        <v>291</v>
+      </c>
+      <c r="C629" s="8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" s="7">
+        <v>33</v>
+      </c>
+      <c r="C630" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" s="7">
+        <v>35</v>
+      </c>
+      <c r="C631" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" s="7">
+        <v>35</v>
+      </c>
+      <c r="C632" s="8">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" s="7">
+        <v>176</v>
+      </c>
+      <c r="C633" s="8">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" s="7">
+        <v>32</v>
+      </c>
+      <c r="C634" s="8">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" s="7">
+        <v>72</v>
+      </c>
+      <c r="C635" s="8">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" s="7">
+        <v>337</v>
+      </c>
+      <c r="C636" s="8">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" s="7">
+        <v>311</v>
+      </c>
+      <c r="C637" s="8">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" s="7">
+        <v>10</v>
+      </c>
+      <c r="C638" s="8">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" s="7">
+        <v>209</v>
+      </c>
+      <c r="C639" s="8">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" s="7">
+        <v>10</v>
+      </c>
+      <c r="C640" s="8">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" s="7">
+        <v>10</v>
+      </c>
+      <c r="C641" s="8">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" s="7">
+        <v>485</v>
+      </c>
+      <c r="C642" s="8">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" s="7">
+        <v>242</v>
+      </c>
+      <c r="C643" s="8">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" s="7">
+        <v>43</v>
+      </c>
+      <c r="C644" s="8">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" s="7">
+        <v>273</v>
+      </c>
+      <c r="C645" s="8">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" s="7">
+        <v>42</v>
+      </c>
+      <c r="C646" s="8">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" s="7">
+        <v>72</v>
+      </c>
+      <c r="C647" s="8">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" s="7">
+        <v>70</v>
+      </c>
+      <c r="C648" s="8">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" s="7">
+        <v>70</v>
+      </c>
+      <c r="C649" s="8">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" s="7">
+        <v>127</v>
+      </c>
+      <c r="C650" s="8">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" s="7">
+        <v>126</v>
+      </c>
+      <c r="C651" s="8">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" s="7">
+        <v>59</v>
+      </c>
+      <c r="C652" s="8">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" s="7">
+        <v>418</v>
+      </c>
+      <c r="C653" s="8">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" s="7">
+        <v>418</v>
+      </c>
+      <c r="C654" s="8">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" s="7">
+        <v>393</v>
+      </c>
+      <c r="C655" s="8">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" s="7">
+        <v>17</v>
+      </c>
+      <c r="C656" s="8">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" s="7">
+        <v>121</v>
+      </c>
+      <c r="C657" s="8">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" s="7">
+        <v>141</v>
+      </c>
+      <c r="C658" s="8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" s="7">
+        <v>141</v>
+      </c>
+      <c r="C659" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" s="7">
+        <v>123</v>
+      </c>
+      <c r="C660" s="8">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepts_features.xlsx
+++ b/raw/Concepts_features.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="46">
       <c r="B46" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C46" s="8">
         <v>313</v>
@@ -5379,6 +5379,62 @@
         <v>107</v>
       </c>
     </row>
+    <row r="661">
+      <c r="B661" s="7">
+        <v>186</v>
+      </c>
+      <c r="C661" s="8">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="B662" s="7">
+        <v>260</v>
+      </c>
+      <c r="C662" s="8">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="B663" s="7">
+        <v>186</v>
+      </c>
+      <c r="C663" s="8">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="B664" s="7">
+        <v>88</v>
+      </c>
+      <c r="C664" s="8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="B665" s="7">
+        <v>95</v>
+      </c>
+      <c r="C665" s="8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="B666" s="7">
+        <v>35</v>
+      </c>
+      <c r="C666" s="8">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="B667" s="7">
+        <v>176</v>
+      </c>
+      <c r="C667" s="8">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>